--- a/research/traditional_assets/database/data/australia/australia_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_packaging_container.xlsx
@@ -1537,7 +1537,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1674,22 +1674,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07251485179629544</v>
+        <v>0.07232880724090654</v>
       </c>
       <c r="C2">
-        <v>2786.177423429391</v>
+        <v>2767.906209533541</v>
       </c>
       <c r="D2">
-        <v>2602.877423429391</v>
+        <v>2621.131209533541</v>
       </c>
       <c r="E2">
-        <v>-1613.2</v>
+        <v>-1576.675</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>36.525</v>
       </c>
       <c r="G2">
         <v>183.3</v>
@@ -1710,28 +1710,28 @@
         <v>360.85</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.8372075</v>
       </c>
       <c r="N2">
-        <v>360.85</v>
+        <v>359.0127925</v>
       </c>
       <c r="O2">
-        <v>108.255</v>
+        <v>107.70383775</v>
       </c>
       <c r="P2">
-        <v>252.595</v>
+        <v>251.30895475</v>
       </c>
       <c r="Q2">
-        <v>348.4949999999999</v>
+        <v>347.20895475</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07251485179629544</v>
+        <v>0.07270374468778439</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6213335955608404</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>196.4122179993278</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1756,22 +1756,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07232880724090654</v>
+        <v>0.07214276268551766</v>
       </c>
       <c r="C3">
-        <v>2767.906209533541</v>
+        <v>2749.892828694947</v>
       </c>
       <c r="D3">
-        <v>2621.131209533541</v>
+        <v>2639.642828694947</v>
       </c>
       <c r="E3">
-        <v>-1576.675</v>
+        <v>-1540.15</v>
       </c>
       <c r="F3">
-        <v>36.525</v>
+        <v>73.05</v>
       </c>
       <c r="G3">
         <v>183.3</v>
@@ -1792,28 +1792,28 @@
         <v>360.85</v>
       </c>
       <c r="M3">
-        <v>1.8372075</v>
+        <v>3.674415</v>
       </c>
       <c r="N3">
-        <v>359.0127925</v>
+        <v>357.175585</v>
       </c>
       <c r="O3">
-        <v>107.70383775</v>
+        <v>107.1526755</v>
       </c>
       <c r="P3">
-        <v>251.30895475</v>
+        <v>250.0229095</v>
       </c>
       <c r="Q3">
-        <v>347.20895475</v>
+        <v>345.9229094999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07270374468778439</v>
+        <v>0.0728964925362425</v>
       </c>
       <c r="T3">
-        <v>0.6213335955608404</v>
+        <v>0.6257850470263859</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>196.4122179993278</v>
+        <v>98.20610899966388</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1838,22 +1838,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07214276268551766</v>
+        <v>0.07195671813012877</v>
       </c>
       <c r="C4">
-        <v>2749.892828694947</v>
+        <v>2732.142782571303</v>
       </c>
       <c r="D4">
-        <v>2639.642828694947</v>
+        <v>2658.417782571302</v>
       </c>
       <c r="E4">
-        <v>-1540.15</v>
+        <v>-1503.625</v>
       </c>
       <c r="F4">
-        <v>73.05</v>
+        <v>109.575</v>
       </c>
       <c r="G4">
         <v>183.3</v>
@@ -1874,28 +1874,28 @@
         <v>360.85</v>
       </c>
       <c r="M4">
-        <v>3.674415</v>
+        <v>5.5116225</v>
       </c>
       <c r="N4">
-        <v>357.175585</v>
+        <v>355.3383775</v>
       </c>
       <c r="O4">
-        <v>107.1526755</v>
+        <v>106.60151325</v>
       </c>
       <c r="P4">
-        <v>250.0229095</v>
+        <v>248.73686425</v>
       </c>
       <c r="Q4">
-        <v>345.9229094999999</v>
+        <v>344.63686425</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0728964925362425</v>
+        <v>0.07309321456714307</v>
       </c>
       <c r="T4">
-        <v>0.6257850470263859</v>
+        <v>0.6303282809963757</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>98.20610899966388</v>
+        <v>65.47073933310926</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1920,22 +1920,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07195671813012877</v>
+        <v>0.07177067357473989</v>
       </c>
       <c r="C5">
-        <v>2732.142782571303</v>
+        <v>2714.661730467881</v>
       </c>
       <c r="D5">
-        <v>2658.417782571302</v>
+        <v>2677.46173046788</v>
       </c>
       <c r="E5">
-        <v>-1503.625</v>
+        <v>-1467.1</v>
       </c>
       <c r="F5">
-        <v>109.575</v>
+        <v>146.1</v>
       </c>
       <c r="G5">
         <v>183.3</v>
@@ -1956,28 +1956,28 @@
         <v>360.85</v>
       </c>
       <c r="M5">
-        <v>5.5116225</v>
+        <v>7.34883</v>
       </c>
       <c r="N5">
-        <v>355.3383775</v>
+        <v>353.5011699999999</v>
       </c>
       <c r="O5">
-        <v>106.60151325</v>
+        <v>106.050351</v>
       </c>
       <c r="P5">
-        <v>248.73686425</v>
+        <v>247.450819</v>
       </c>
       <c r="Q5">
-        <v>344.63686425</v>
+        <v>343.3508189999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07309321456714307</v>
+        <v>0.07329403497368739</v>
       </c>
       <c r="T5">
-        <v>0.6303282809963757</v>
+        <v>0.6349661656740735</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.47073933310926</v>
+        <v>49.10305449983194</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2002,22 +2002,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07177067357473989</v>
+        <v>0.071584629019351</v>
       </c>
       <c r="C6">
-        <v>2714.661730467881</v>
+        <v>2697.455495024928</v>
       </c>
       <c r="D6">
-        <v>2677.46173046788</v>
+        <v>2696.780495024927</v>
       </c>
       <c r="E6">
-        <v>-1467.1</v>
+        <v>-1430.575</v>
       </c>
       <c r="F6">
-        <v>146.1</v>
+        <v>182.625</v>
       </c>
       <c r="G6">
         <v>183.3</v>
@@ -2038,28 +2038,28 @@
         <v>360.85</v>
       </c>
       <c r="M6">
-        <v>7.34883</v>
+        <v>9.186037499999999</v>
       </c>
       <c r="N6">
-        <v>353.5011699999999</v>
+        <v>351.6639625</v>
       </c>
       <c r="O6">
-        <v>106.050351</v>
+        <v>105.49918875</v>
       </c>
       <c r="P6">
-        <v>247.450819</v>
+        <v>246.16477375</v>
       </c>
       <c r="Q6">
-        <v>343.3508189999999</v>
+        <v>342.06477375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07329403497368739</v>
+        <v>0.07349908317826422</v>
       </c>
       <c r="T6">
-        <v>0.6349661656740735</v>
+        <v>0.6397016900291966</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.10305449983194</v>
+        <v>39.28244359986556</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2084,22 +2084,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.071584629019351</v>
+        <v>0.07139858446396211</v>
       </c>
       <c r="C7">
-        <v>2697.455495024928</v>
+        <v>2680.53006815307</v>
       </c>
       <c r="D7">
-        <v>2696.780495024927</v>
+        <v>2716.38006815307</v>
       </c>
       <c r="E7">
-        <v>-1430.575</v>
+        <v>-1394.05</v>
       </c>
       <c r="F7">
-        <v>182.625</v>
+        <v>219.15</v>
       </c>
       <c r="G7">
         <v>183.3</v>
@@ -2120,28 +2120,28 @@
         <v>360.85</v>
       </c>
       <c r="M7">
-        <v>9.186037499999999</v>
+        <v>11.023245</v>
       </c>
       <c r="N7">
-        <v>351.6639625</v>
+        <v>349.826755</v>
       </c>
       <c r="O7">
-        <v>105.49918875</v>
+        <v>104.9480265</v>
       </c>
       <c r="P7">
-        <v>246.16477375</v>
+        <v>244.8787285</v>
       </c>
       <c r="Q7">
-        <v>342.06477375</v>
+        <v>340.7787284999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07349908317826422</v>
+        <v>0.07370849411059799</v>
       </c>
       <c r="T7">
-        <v>0.6397016900291966</v>
+        <v>0.6445379702216627</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.28244359986556</v>
+        <v>32.73536966655463</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2166,22 +2166,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07139858446396211</v>
+        <v>0.07121253990857324</v>
       </c>
       <c r="C8">
-        <v>2680.53006815307</v>
+        <v>2663.891617229427</v>
       </c>
       <c r="D8">
-        <v>2716.38006815307</v>
+        <v>2736.266617229427</v>
       </c>
       <c r="E8">
-        <v>-1394.05</v>
+        <v>-1357.525</v>
       </c>
       <c r="F8">
-        <v>219.15</v>
+        <v>255.675</v>
       </c>
       <c r="G8">
         <v>183.3</v>
@@ -2202,28 +2202,28 @@
         <v>360.85</v>
       </c>
       <c r="M8">
-        <v>11.023245</v>
+        <v>12.8604525</v>
       </c>
       <c r="N8">
-        <v>349.826755</v>
+        <v>347.9895475</v>
       </c>
       <c r="O8">
-        <v>104.9480265</v>
+        <v>104.39686425</v>
       </c>
       <c r="P8">
-        <v>244.8787285</v>
+        <v>243.59268325</v>
       </c>
       <c r="Q8">
-        <v>340.7787284999999</v>
+        <v>339.49268325</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07370849411059799</v>
+        <v>0.07392240850384219</v>
       </c>
       <c r="T8">
-        <v>0.6445379702216627</v>
+        <v>0.6494782564397733</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.73536966655463</v>
+        <v>28.05888828561825</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2248,22 +2248,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07121253990857322</v>
+        <v>0.07102649535318435</v>
       </c>
       <c r="C9">
-        <v>2663.891617229429</v>
+        <v>2647.546491567923</v>
       </c>
       <c r="D9">
-        <v>2736.266617229429</v>
+        <v>2756.446491567923</v>
       </c>
       <c r="E9">
-        <v>-1357.525</v>
+        <v>-1321</v>
       </c>
       <c r="F9">
-        <v>255.675</v>
+        <v>292.2</v>
       </c>
       <c r="G9">
         <v>183.3</v>
@@ -2284,28 +2284,28 @@
         <v>360.85</v>
       </c>
       <c r="M9">
-        <v>12.8604525</v>
+        <v>14.69766</v>
       </c>
       <c r="N9">
-        <v>347.9895475</v>
+        <v>346.15234</v>
       </c>
       <c r="O9">
-        <v>104.39686425</v>
+        <v>103.845702</v>
       </c>
       <c r="P9">
-        <v>243.59268325</v>
+        <v>242.306638</v>
       </c>
       <c r="Q9">
-        <v>339.49268325</v>
+        <v>338.206638</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07392240850384219</v>
+        <v>0.07414097320998299</v>
       </c>
       <c r="T9">
-        <v>0.6494782564397733</v>
+        <v>0.6545259401843646</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.05888828561825</v>
+        <v>24.55152724991597</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2330,22 +2330,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07102649535318435</v>
+        <v>0.07084045079779547</v>
       </c>
       <c r="C10">
-        <v>2647.546491567923</v>
+        <v>2631.501229178004</v>
       </c>
       <c r="D10">
-        <v>2756.446491567923</v>
+        <v>2776.926229178004</v>
       </c>
       <c r="E10">
-        <v>-1321</v>
+        <v>-1284.475</v>
       </c>
       <c r="F10">
-        <v>292.2</v>
+        <v>328.725</v>
       </c>
       <c r="G10">
         <v>183.3</v>
@@ -2366,28 +2366,28 @@
         <v>360.85</v>
       </c>
       <c r="M10">
-        <v>14.69766</v>
+        <v>16.5348675</v>
       </c>
       <c r="N10">
-        <v>346.15234</v>
+        <v>344.3151324999999</v>
       </c>
       <c r="O10">
-        <v>103.845702</v>
+        <v>103.29453975</v>
       </c>
       <c r="P10">
-        <v>242.306638</v>
+        <v>241.02059275</v>
       </c>
       <c r="Q10">
-        <v>338.206638</v>
+        <v>336.92059275</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07414097320998299</v>
+        <v>0.07436434153603896</v>
       </c>
       <c r="T10">
-        <v>0.6545259401843646</v>
+        <v>0.6596845620332324</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.55152724991597</v>
+        <v>21.82357977770309</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2412,22 +2412,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07084045079779547</v>
+        <v>0.07065440624240657</v>
       </c>
       <c r="C11">
-        <v>2631.501229178004</v>
+        <v>2615.762563826937</v>
       </c>
       <c r="D11">
-        <v>2776.926229178004</v>
+        <v>2797.712563826937</v>
       </c>
       <c r="E11">
-        <v>-1284.475</v>
+        <v>-1247.95</v>
       </c>
       <c r="F11">
-        <v>328.725</v>
+        <v>365.2499999999999</v>
       </c>
       <c r="G11">
         <v>183.3</v>
@@ -2448,28 +2448,28 @@
         <v>360.85</v>
       </c>
       <c r="M11">
-        <v>16.5348675</v>
+        <v>18.372075</v>
       </c>
       <c r="N11">
-        <v>344.3151324999999</v>
+        <v>342.477925</v>
       </c>
       <c r="O11">
-        <v>103.29453975</v>
+        <v>102.7433775</v>
       </c>
       <c r="P11">
-        <v>241.02059275</v>
+        <v>239.7345475</v>
       </c>
       <c r="Q11">
-        <v>336.92059275</v>
+        <v>335.6345474999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07436434153603896</v>
+        <v>0.07459267360267396</v>
       </c>
       <c r="T11">
-        <v>0.6596845620332324</v>
+        <v>0.6649578199231864</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.82357977770309</v>
+        <v>19.64122179993278</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2494,22 +2494,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07065440624240657</v>
+        <v>0.0704683616870177</v>
       </c>
       <c r="C12">
-        <v>2615.762563826937</v>
+        <v>2600.337432421654</v>
       </c>
       <c r="D12">
-        <v>2797.712563826937</v>
+        <v>2818.812432421654</v>
       </c>
       <c r="E12">
-        <v>-1247.95</v>
+        <v>-1211.425</v>
       </c>
       <c r="F12">
-        <v>365.25</v>
+        <v>401.775</v>
       </c>
       <c r="G12">
         <v>183.3</v>
@@ -2530,28 +2530,28 @@
         <v>360.85</v>
       </c>
       <c r="M12">
-        <v>18.372075</v>
+        <v>20.2092825</v>
       </c>
       <c r="N12">
-        <v>342.477925</v>
+        <v>340.6407175</v>
       </c>
       <c r="O12">
-        <v>102.7433775</v>
+        <v>102.19221525</v>
       </c>
       <c r="P12">
-        <v>239.7345475</v>
+        <v>238.44850225</v>
       </c>
       <c r="Q12">
-        <v>335.6345474999999</v>
+        <v>334.34850225</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07459267360267396</v>
+        <v>0.07482613672698617</v>
       </c>
       <c r="T12">
-        <v>0.6649578199231864</v>
+        <v>0.6703495779904426</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.64122179993278</v>
+        <v>17.85565618175707</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2576,22 +2576,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0704683616870177</v>
+        <v>0.07028231713162879</v>
       </c>
       <c r="C13">
-        <v>2600.337432421654</v>
+        <v>2585.23298272721</v>
       </c>
       <c r="D13">
-        <v>2818.812432421654</v>
+        <v>2840.23298272721</v>
       </c>
       <c r="E13">
-        <v>-1211.425</v>
+        <v>-1174.9</v>
       </c>
       <c r="F13">
-        <v>401.775</v>
+        <v>438.3</v>
       </c>
       <c r="G13">
         <v>183.3</v>
@@ -2612,28 +2612,28 @@
         <v>360.85</v>
       </c>
       <c r="M13">
-        <v>20.2092825</v>
+        <v>22.04649</v>
       </c>
       <c r="N13">
-        <v>340.6407175</v>
+        <v>338.80351</v>
       </c>
       <c r="O13">
-        <v>102.19221525</v>
+        <v>101.641053</v>
       </c>
       <c r="P13">
-        <v>238.44850225</v>
+        <v>237.162457</v>
       </c>
       <c r="Q13">
-        <v>334.34850225</v>
+        <v>333.0624569999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07482613672698617</v>
+        <v>0.07506490583139636</v>
       </c>
       <c r="T13">
-        <v>0.6703495779904426</v>
+        <v>0.6758638760137728</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.85565618175707</v>
+        <v>16.36768483327732</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2658,22 +2658,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07028231713162879</v>
+        <v>0.07009627257623992</v>
       </c>
       <c r="C14">
-        <v>2585.23298272721</v>
+        <v>2570.456581439798</v>
       </c>
       <c r="D14">
-        <v>2840.23298272721</v>
+        <v>2861.981581439798</v>
       </c>
       <c r="E14">
-        <v>-1174.9</v>
+        <v>-1138.375</v>
       </c>
       <c r="F14">
-        <v>438.3</v>
+        <v>474.825</v>
       </c>
       <c r="G14">
         <v>183.3</v>
@@ -2694,28 +2694,28 @@
         <v>360.85</v>
       </c>
       <c r="M14">
-        <v>22.04649</v>
+        <v>23.8836975</v>
       </c>
       <c r="N14">
-        <v>338.80351</v>
+        <v>336.9663025</v>
       </c>
       <c r="O14">
-        <v>101.641053</v>
+        <v>101.08989075</v>
       </c>
       <c r="P14">
-        <v>237.162457</v>
+        <v>235.87641175</v>
       </c>
       <c r="Q14">
-        <v>333.0624569999999</v>
+        <v>331.77641175</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07506490583139636</v>
+        <v>0.07530916388073552</v>
       </c>
       <c r="T14">
-        <v>0.6758638760137728</v>
+        <v>0.6815049395089038</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.36768483327732</v>
+        <v>15.10863215379445</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2740,22 +2740,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07009627257623992</v>
+        <v>0.06991022802085102</v>
       </c>
       <c r="C15">
-        <v>2570.456581439798</v>
+        <v>2556.015822633606</v>
       </c>
       <c r="D15">
-        <v>2861.981581439798</v>
+        <v>2884.065822633606</v>
       </c>
       <c r="E15">
-        <v>-1138.375</v>
+        <v>-1101.85</v>
       </c>
       <c r="F15">
-        <v>474.825</v>
+        <v>511.35</v>
       </c>
       <c r="G15">
         <v>183.3</v>
@@ -2776,28 +2776,28 @@
         <v>360.85</v>
       </c>
       <c r="M15">
-        <v>23.8836975</v>
+        <v>25.720905</v>
       </c>
       <c r="N15">
-        <v>336.9663025</v>
+        <v>335.1290949999999</v>
       </c>
       <c r="O15">
-        <v>101.08989075</v>
+        <v>100.5387285</v>
       </c>
       <c r="P15">
-        <v>235.87641175</v>
+        <v>234.5903665</v>
       </c>
       <c r="Q15">
-        <v>331.77641175</v>
+        <v>330.4903664999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07530916388073552</v>
+        <v>0.07555910234982677</v>
       </c>
       <c r="T15">
-        <v>0.6815049395089038</v>
+        <v>0.6872771905271773</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.10863215379445</v>
+        <v>14.02944414280913</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2822,22 +2822,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06991022802085102</v>
+        <v>0.06972418346546214</v>
       </c>
       <c r="C16">
-        <v>2556.015822633606</v>
+        <v>2541.918536601723</v>
       </c>
       <c r="D16">
-        <v>2884.065822633606</v>
+        <v>2906.493536601723</v>
       </c>
       <c r="E16">
-        <v>-1101.85</v>
+        <v>-1065.325</v>
       </c>
       <c r="F16">
-        <v>511.35</v>
+        <v>547.8750000000001</v>
       </c>
       <c r="G16">
         <v>183.3</v>
@@ -2858,28 +2858,28 @@
         <v>360.85</v>
       </c>
       <c r="M16">
-        <v>25.720905</v>
+        <v>27.5581125</v>
       </c>
       <c r="N16">
-        <v>335.1290949999999</v>
+        <v>333.2918875</v>
       </c>
       <c r="O16">
-        <v>100.5387285</v>
+        <v>99.98756624999999</v>
       </c>
       <c r="P16">
-        <v>234.5903665</v>
+        <v>233.30432125</v>
       </c>
       <c r="Q16">
-        <v>330.4903664999999</v>
+        <v>329.20432125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07555910234982677</v>
+        <v>0.07581492172407311</v>
       </c>
       <c r="T16">
-        <v>0.6872771905271773</v>
+        <v>0.693185259216469</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.02944414280913</v>
+        <v>13.09414786662185</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2904,22 +2904,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06972418346546214</v>
+        <v>0.06970613891007325</v>
       </c>
       <c r="C17">
-        <v>2541.918536601723</v>
+        <v>2507.58738245052</v>
       </c>
       <c r="D17">
-        <v>2906.493536601723</v>
+        <v>2908.68738245052</v>
       </c>
       <c r="E17">
-        <v>-1065.325</v>
+        <v>-1028.8</v>
       </c>
       <c r="F17">
-        <v>547.875</v>
+        <v>584.4</v>
       </c>
       <c r="G17">
         <v>183.3</v>
@@ -2940,45 +2940,45 @@
         <v>360.85</v>
       </c>
       <c r="M17">
-        <v>27.5581125</v>
+        <v>30.27192</v>
       </c>
       <c r="N17">
-        <v>333.2918875</v>
+        <v>330.5780799999999</v>
       </c>
       <c r="O17">
-        <v>99.98756624999999</v>
+        <v>99.17342399999998</v>
       </c>
       <c r="P17">
-        <v>233.30432125</v>
+        <v>231.404656</v>
       </c>
       <c r="Q17">
-        <v>329.20432125</v>
+        <v>327.3046559999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07581492172407311</v>
+        <v>0.0760768320358015</v>
       </c>
       <c r="T17">
-        <v>0.693185259216469</v>
+        <v>0.6992339962078867</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.09414786662185</v>
+        <v>11.92028784431248</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2986,22 +2986,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06970613891007325</v>
+        <v>0.06953059435468435</v>
       </c>
       <c r="C18">
-        <v>2507.58738245052</v>
+        <v>2492.579088930179</v>
       </c>
       <c r="D18">
-        <v>2908.68738245052</v>
+        <v>2930.204088930179</v>
       </c>
       <c r="E18">
-        <v>-1028.8</v>
+        <v>-992.275</v>
       </c>
       <c r="F18">
-        <v>584.4</v>
+        <v>620.9250000000001</v>
       </c>
       <c r="G18">
         <v>183.3</v>
@@ -3022,28 +3022,28 @@
         <v>360.85</v>
       </c>
       <c r="M18">
-        <v>30.27192</v>
+        <v>32.163915</v>
       </c>
       <c r="N18">
-        <v>330.5780799999999</v>
+        <v>328.6860849999999</v>
       </c>
       <c r="O18">
-        <v>99.17342399999998</v>
+        <v>98.60582549999998</v>
       </c>
       <c r="P18">
-        <v>231.404656</v>
+        <v>230.0802595</v>
       </c>
       <c r="Q18">
-        <v>327.3046559999999</v>
+        <v>325.9802594999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0760768320358015</v>
+        <v>0.07634505343937875</v>
       </c>
       <c r="T18">
-        <v>0.6992339962078867</v>
+        <v>0.7054284858978929</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.92028784431248</v>
+        <v>11.21909444170586</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3068,22 +3068,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06953059435468435</v>
+        <v>0.06935504979929548</v>
       </c>
       <c r="C19">
-        <v>2492.579088930179</v>
+        <v>2477.891502918805</v>
       </c>
       <c r="D19">
-        <v>2930.204088930179</v>
+        <v>2952.041502918804</v>
       </c>
       <c r="E19">
-        <v>-992.275</v>
+        <v>-955.75</v>
       </c>
       <c r="F19">
-        <v>620.9250000000001</v>
+        <v>657.45</v>
       </c>
       <c r="G19">
         <v>183.3</v>
@@ -3104,28 +3104,28 @@
         <v>360.85</v>
       </c>
       <c r="M19">
-        <v>32.163915</v>
+        <v>34.05591</v>
       </c>
       <c r="N19">
-        <v>328.6860849999999</v>
+        <v>326.79409</v>
       </c>
       <c r="O19">
-        <v>98.60582549999998</v>
+        <v>98.03822699999999</v>
       </c>
       <c r="P19">
-        <v>230.0802595</v>
+        <v>228.755863</v>
       </c>
       <c r="Q19">
-        <v>325.9802594999999</v>
+        <v>324.655863</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07634505343937875</v>
+        <v>0.07661981682840913</v>
       </c>
       <c r="T19">
-        <v>0.7054284858978929</v>
+        <v>0.7117740607022892</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.21909444170586</v>
+        <v>10.59581141716665</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3150,22 +3150,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06935504979929549</v>
+        <v>0.06917950524390661</v>
       </c>
       <c r="C20">
-        <v>2477.891502918803</v>
+        <v>2463.531848494475</v>
       </c>
       <c r="D20">
-        <v>2952.041502918803</v>
+        <v>2974.206848494475</v>
       </c>
       <c r="E20">
-        <v>-955.7500000000001</v>
+        <v>-919.225</v>
       </c>
       <c r="F20">
-        <v>657.4499999999999</v>
+        <v>693.975</v>
       </c>
       <c r="G20">
         <v>183.3</v>
@@ -3186,28 +3186,28 @@
         <v>360.85</v>
       </c>
       <c r="M20">
-        <v>34.05591</v>
+        <v>35.947905</v>
       </c>
       <c r="N20">
-        <v>326.79409</v>
+        <v>324.902095</v>
       </c>
       <c r="O20">
-        <v>98.03822699999999</v>
+        <v>97.47062849999999</v>
       </c>
       <c r="P20">
-        <v>228.755863</v>
+        <v>227.4314665</v>
       </c>
       <c r="Q20">
-        <v>324.655863</v>
+        <v>323.3314665</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07661981682840913</v>
+        <v>0.07690136449865012</v>
       </c>
       <c r="T20">
-        <v>0.7117740607022892</v>
+        <v>0.7182763163660535</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.59581141716665</v>
+        <v>10.03813713205262</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3232,22 +3232,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06917950524390661</v>
+        <v>0.06924196068851772</v>
       </c>
       <c r="C21">
-        <v>2463.531848494475</v>
+        <v>2419.082792415875</v>
       </c>
       <c r="D21">
-        <v>2974.206848494475</v>
+        <v>2966.282792415875</v>
       </c>
       <c r="E21">
-        <v>-919.225</v>
+        <v>-882.7</v>
       </c>
       <c r="F21">
-        <v>693.975</v>
+        <v>730.5</v>
       </c>
       <c r="G21">
         <v>183.3</v>
@@ -3268,45 +3268,45 @@
         <v>360.85</v>
       </c>
       <c r="M21">
-        <v>35.947905</v>
+        <v>39.08175</v>
       </c>
       <c r="N21">
-        <v>324.902095</v>
+        <v>321.76825</v>
       </c>
       <c r="O21">
-        <v>97.47062849999999</v>
+        <v>96.53047499999998</v>
       </c>
       <c r="P21">
-        <v>227.4314665</v>
+        <v>225.237775</v>
       </c>
       <c r="Q21">
-        <v>323.3314665</v>
+        <v>321.137775</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07690136449865012</v>
+        <v>0.07718995086064714</v>
       </c>
       <c r="T21">
-        <v>0.7182763163660535</v>
+        <v>0.724941128421412</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.03813713205262</v>
+        <v>9.233209874174007</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3314,22 +3314,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06924196068851772</v>
+        <v>0.06907831613312883</v>
       </c>
       <c r="C22">
-        <v>2419.082792415875</v>
+        <v>2403.410504697404</v>
       </c>
       <c r="D22">
-        <v>2966.282792415875</v>
+        <v>2987.135504697404</v>
       </c>
       <c r="E22">
-        <v>-882.7</v>
+        <v>-846.175</v>
       </c>
       <c r="F22">
-        <v>730.5</v>
+        <v>767.0250000000001</v>
       </c>
       <c r="G22">
         <v>183.3</v>
@@ -3350,28 +3350,28 @@
         <v>360.85</v>
       </c>
       <c r="M22">
-        <v>39.08175</v>
+        <v>41.03583750000001</v>
       </c>
       <c r="N22">
-        <v>321.76825</v>
+        <v>319.8141625</v>
       </c>
       <c r="O22">
-        <v>96.53047499999998</v>
+        <v>95.94424874999999</v>
       </c>
       <c r="P22">
-        <v>225.237775</v>
+        <v>223.86991375</v>
       </c>
       <c r="Q22">
-        <v>321.137775</v>
+        <v>319.7699137499999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07718995086064714</v>
+        <v>0.07748584320649218</v>
       </c>
       <c r="T22">
-        <v>0.724941128421412</v>
+        <v>0.7317746698958935</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.233209874174007</v>
+        <v>8.793533213499053</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3396,22 +3396,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06907831613312883</v>
+        <v>0.06891467157773994</v>
       </c>
       <c r="C23">
-        <v>2403.410504697404</v>
+        <v>2388.0334781786</v>
       </c>
       <c r="D23">
-        <v>2987.135504697404</v>
+        <v>3008.2834781786</v>
       </c>
       <c r="E23">
-        <v>-846.1750000000001</v>
+        <v>-809.6500000000001</v>
       </c>
       <c r="F23">
-        <v>767.025</v>
+        <v>803.55</v>
       </c>
       <c r="G23">
         <v>183.3</v>
@@ -3432,28 +3432,28 @@
         <v>360.85</v>
       </c>
       <c r="M23">
-        <v>41.0358375</v>
+        <v>42.989925</v>
       </c>
       <c r="N23">
-        <v>319.8141625</v>
+        <v>317.8600749999999</v>
       </c>
       <c r="O23">
-        <v>95.94424874999999</v>
+        <v>95.35802249999998</v>
       </c>
       <c r="P23">
-        <v>223.86991375</v>
+        <v>222.5020525</v>
       </c>
       <c r="Q23">
-        <v>319.7699137499999</v>
+        <v>318.4020525</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07748584320649218</v>
+        <v>0.07778932253556402</v>
       </c>
       <c r="T23">
-        <v>0.7317746698958932</v>
+        <v>0.7387834303825409</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.793533213499053</v>
+        <v>8.393827158340006</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3478,22 +3478,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06891467157773994</v>
+        <v>0.06875102702235106</v>
       </c>
       <c r="C24">
-        <v>2388.0334781786</v>
+        <v>2372.958028640582</v>
       </c>
       <c r="D24">
-        <v>3008.2834781786</v>
+        <v>3029.733028640582</v>
       </c>
       <c r="E24">
-        <v>-809.6500000000001</v>
+        <v>-773.125</v>
       </c>
       <c r="F24">
-        <v>803.55</v>
+        <v>840.075</v>
       </c>
       <c r="G24">
         <v>183.3</v>
@@ -3514,28 +3514,28 @@
         <v>360.85</v>
       </c>
       <c r="M24">
-        <v>42.989925</v>
+        <v>44.9440125</v>
       </c>
       <c r="N24">
-        <v>317.8600749999999</v>
+        <v>315.9059875</v>
       </c>
       <c r="O24">
-        <v>95.35802249999998</v>
+        <v>94.77179624999999</v>
       </c>
       <c r="P24">
-        <v>222.5020525</v>
+        <v>221.13419125</v>
       </c>
       <c r="Q24">
-        <v>318.4020525</v>
+        <v>317.0341912499999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07778932253556402</v>
+        <v>0.07810068444461175</v>
       </c>
       <c r="T24">
-        <v>0.7387834303825409</v>
+        <v>0.7459742365961144</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.393827158340006</v>
+        <v>8.028878151455658</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3560,22 +3560,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06875102702235106</v>
+        <v>0.06858738246696217</v>
       </c>
       <c r="C25">
-        <v>2372.958028640582</v>
+        <v>2358.190653288247</v>
       </c>
       <c r="D25">
-        <v>3029.733028640582</v>
+        <v>3051.490653288246</v>
       </c>
       <c r="E25">
-        <v>-773.125</v>
+        <v>-736.6</v>
       </c>
       <c r="F25">
-        <v>840.075</v>
+        <v>876.6</v>
       </c>
       <c r="G25">
         <v>183.3</v>
@@ -3596,28 +3596,28 @@
         <v>360.85</v>
       </c>
       <c r="M25">
-        <v>44.9440125</v>
+        <v>46.8981</v>
       </c>
       <c r="N25">
-        <v>315.9059875</v>
+        <v>313.9519</v>
       </c>
       <c r="O25">
-        <v>94.77179624999999</v>
+        <v>94.18556999999998</v>
       </c>
       <c r="P25">
-        <v>221.13419125</v>
+        <v>219.76633</v>
       </c>
       <c r="Q25">
-        <v>317.0341912499999</v>
+        <v>315.66633</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07810068444461175</v>
+        <v>0.07842024008810811</v>
       </c>
       <c r="T25">
-        <v>0.7459742365961144</v>
+        <v>0.7533542745521504</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.028878151455658</v>
+        <v>7.694341561811672</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3642,22 +3642,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06858738246696217</v>
+        <v>0.06856373791157329</v>
       </c>
       <c r="C26">
-        <v>2358.190653288247</v>
+        <v>2324.835217972684</v>
       </c>
       <c r="D26">
-        <v>3051.490653288246</v>
+        <v>3054.660217972684</v>
       </c>
       <c r="E26">
-        <v>-736.6</v>
+        <v>-700.075</v>
       </c>
       <c r="F26">
-        <v>876.6</v>
+        <v>913.125</v>
       </c>
       <c r="G26">
         <v>183.3</v>
@@ -3678,45 +3678,45 @@
         <v>360.85</v>
       </c>
       <c r="M26">
-        <v>46.8981</v>
+        <v>49.5826875</v>
       </c>
       <c r="N26">
-        <v>313.9519</v>
+        <v>311.2673124999999</v>
       </c>
       <c r="O26">
-        <v>94.18556999999998</v>
+        <v>93.38019374999998</v>
       </c>
       <c r="P26">
-        <v>219.76633</v>
+        <v>217.88711875</v>
       </c>
       <c r="Q26">
-        <v>315.66633</v>
+        <v>313.7871187499999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07842024008810811</v>
+        <v>0.07874831721543105</v>
       </c>
       <c r="T26">
-        <v>0.7533542745521504</v>
+        <v>0.7609311135203474</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.694341561811672</v>
+        <v>7.277741852940101</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3724,22 +3724,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06856373791157329</v>
+        <v>0.06840569335618438</v>
       </c>
       <c r="C27">
-        <v>2324.835217972684</v>
+        <v>2309.666449272779</v>
       </c>
       <c r="D27">
-        <v>3054.660217972684</v>
+        <v>3076.016449272779</v>
       </c>
       <c r="E27">
-        <v>-700.075</v>
+        <v>-663.5500000000001</v>
       </c>
       <c r="F27">
-        <v>913.125</v>
+        <v>949.65</v>
       </c>
       <c r="G27">
         <v>183.3</v>
@@ -3760,28 +3760,28 @@
         <v>360.85</v>
       </c>
       <c r="M27">
-        <v>49.5826875</v>
+        <v>51.565995</v>
       </c>
       <c r="N27">
-        <v>311.2673124999999</v>
+        <v>309.284005</v>
       </c>
       <c r="O27">
-        <v>93.38019374999998</v>
+        <v>92.78520149999999</v>
       </c>
       <c r="P27">
-        <v>217.88711875</v>
+        <v>216.4988035</v>
       </c>
       <c r="Q27">
-        <v>313.7871187499999</v>
+        <v>312.3988035</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07874831721543105</v>
+        <v>0.07908526129214107</v>
       </c>
       <c r="T27">
-        <v>0.7609311135203474</v>
+        <v>0.768712731920117</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.277741852940101</v>
+        <v>6.997828704750097</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3806,22 +3806,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06840569335618438</v>
+        <v>0.06824764880079551</v>
       </c>
       <c r="C28">
-        <v>2309.666449272779</v>
+        <v>2294.798401250615</v>
       </c>
       <c r="D28">
-        <v>3076.016449272779</v>
+        <v>3097.673401250615</v>
       </c>
       <c r="E28">
-        <v>-663.5500000000001</v>
+        <v>-627.025</v>
       </c>
       <c r="F28">
-        <v>949.65</v>
+        <v>986.1750000000001</v>
       </c>
       <c r="G28">
         <v>183.3</v>
@@ -3842,28 +3842,28 @@
         <v>360.85</v>
       </c>
       <c r="M28">
-        <v>51.565995</v>
+        <v>53.5493025</v>
       </c>
       <c r="N28">
-        <v>309.284005</v>
+        <v>307.3006975</v>
       </c>
       <c r="O28">
-        <v>92.78520149999999</v>
+        <v>92.19020924999998</v>
       </c>
       <c r="P28">
-        <v>216.4988035</v>
+        <v>215.11048825</v>
       </c>
       <c r="Q28">
-        <v>312.3988035</v>
+        <v>311.01048825</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07908526129214107</v>
+        <v>0.07943143671341851</v>
       </c>
       <c r="T28">
-        <v>0.768712731920117</v>
+        <v>0.7767075453445382</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.997828704750097</v>
+        <v>6.738649863833426</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3888,22 +3888,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06824764880079551</v>
+        <v>0.06808960424540661</v>
       </c>
       <c r="C29">
-        <v>2294.798401250615</v>
+        <v>2280.237470690815</v>
       </c>
       <c r="D29">
-        <v>3097.673401250615</v>
+        <v>3119.637470690815</v>
       </c>
       <c r="E29">
-        <v>-627.025</v>
+        <v>-590.5</v>
       </c>
       <c r="F29">
-        <v>986.1750000000001</v>
+        <v>1022.7</v>
       </c>
       <c r="G29">
         <v>183.3</v>
@@ -3924,28 +3924,28 @@
         <v>360.85</v>
       </c>
       <c r="M29">
-        <v>53.5493025</v>
+        <v>55.53261000000001</v>
       </c>
       <c r="N29">
-        <v>307.3006975</v>
+        <v>305.3173899999999</v>
       </c>
       <c r="O29">
-        <v>92.19020924999998</v>
+        <v>91.59521699999998</v>
       </c>
       <c r="P29">
-        <v>215.11048825</v>
+        <v>213.7221729999999</v>
       </c>
       <c r="Q29">
-        <v>311.01048825</v>
+        <v>309.6221729999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07943143671341851</v>
+        <v>0.0797872281186203</v>
       </c>
       <c r="T29">
-        <v>0.7767075453445382</v>
+        <v>0.7849244369196375</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.738649863833426</v>
+        <v>6.497983797267946</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3970,22 +3970,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06808960424540661</v>
+        <v>0.06793155969001773</v>
       </c>
       <c r="C30">
-        <v>2280.237470690815</v>
+        <v>2265.990237099307</v>
       </c>
       <c r="D30">
-        <v>3119.637470690815</v>
+        <v>3141.915237099307</v>
       </c>
       <c r="E30">
-        <v>-590.5</v>
+        <v>-553.9749999999999</v>
       </c>
       <c r="F30">
-        <v>1022.7</v>
+        <v>1059.225</v>
       </c>
       <c r="G30">
         <v>183.3</v>
@@ -4006,28 +4006,28 @@
         <v>360.85</v>
       </c>
       <c r="M30">
-        <v>55.53261000000001</v>
+        <v>57.51591750000001</v>
       </c>
       <c r="N30">
-        <v>305.3173899999999</v>
+        <v>303.3340825</v>
       </c>
       <c r="O30">
-        <v>91.59521699999998</v>
+        <v>91.00022474999999</v>
       </c>
       <c r="P30">
-        <v>213.7221729999999</v>
+        <v>212.33385775</v>
       </c>
       <c r="Q30">
-        <v>309.6221729999999</v>
+        <v>308.23385775</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0797872281186203</v>
+        <v>0.08015304181692638</v>
       </c>
       <c r="T30">
-        <v>0.7849244369196375</v>
+        <v>0.7933727902292468</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.497983797267946</v>
+        <v>6.273915390465604</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4052,22 +4052,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06793155969001773</v>
+        <v>0.06798351513462884</v>
       </c>
       <c r="C31">
-        <v>2265.990237099307</v>
+        <v>2222.10663761301</v>
       </c>
       <c r="D31">
-        <v>3141.915237099307</v>
+        <v>3134.55663761301</v>
       </c>
       <c r="E31">
-        <v>-553.9750000000001</v>
+        <v>-517.45</v>
       </c>
       <c r="F31">
-        <v>1059.225</v>
+        <v>1095.75</v>
       </c>
       <c r="G31">
         <v>183.3</v>
@@ -4088,45 +4088,45 @@
         <v>360.85</v>
       </c>
       <c r="M31">
-        <v>57.51591749999999</v>
+        <v>60.59497500000001</v>
       </c>
       <c r="N31">
-        <v>303.3340825</v>
+        <v>300.2550249999999</v>
       </c>
       <c r="O31">
-        <v>91.00022474999999</v>
+        <v>90.07650749999998</v>
       </c>
       <c r="P31">
-        <v>212.33385775</v>
+        <v>210.1785174999999</v>
       </c>
       <c r="Q31">
-        <v>308.23385775</v>
+        <v>306.0785174999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08015304181692638</v>
+        <v>0.08052930733518407</v>
       </c>
       <c r="T31">
-        <v>0.7933727902292468</v>
+        <v>0.8020625250619877</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.273915390465604</v>
+        <v>5.955114264837966</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4134,22 +4134,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06798351513462884</v>
+        <v>0.06783247057923997</v>
       </c>
       <c r="C32">
-        <v>2222.10663761301</v>
+        <v>2207.07072627271</v>
       </c>
       <c r="D32">
-        <v>3134.55663761301</v>
+        <v>3156.04572627271</v>
       </c>
       <c r="E32">
-        <v>-517.45</v>
+        <v>-480.925</v>
       </c>
       <c r="F32">
-        <v>1095.75</v>
+        <v>1132.275</v>
       </c>
       <c r="G32">
         <v>183.3</v>
@@ -4170,28 +4170,28 @@
         <v>360.85</v>
       </c>
       <c r="M32">
-        <v>60.59497500000001</v>
+        <v>62.6148075</v>
       </c>
       <c r="N32">
-        <v>300.2550249999999</v>
+        <v>298.2351925</v>
       </c>
       <c r="O32">
-        <v>90.07650749999998</v>
+        <v>89.47055775</v>
       </c>
       <c r="P32">
-        <v>210.1785174999999</v>
+        <v>208.76463475</v>
       </c>
       <c r="Q32">
-        <v>306.0785174999999</v>
+        <v>304.6646347499999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08052930733518407</v>
+        <v>0.08091647910034777</v>
       </c>
       <c r="T32">
-        <v>0.8020625250619877</v>
+        <v>0.8110041362666921</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.955114264837966</v>
+        <v>5.763013804681903</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4216,22 +4216,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06783247057923997</v>
+        <v>0.06768142602385108</v>
       </c>
       <c r="C33">
-        <v>2207.07072627271</v>
+        <v>2192.331487538555</v>
       </c>
       <c r="D33">
-        <v>3156.04572627271</v>
+        <v>3177.831487538554</v>
       </c>
       <c r="E33">
-        <v>-480.925</v>
+        <v>-444.4000000000001</v>
       </c>
       <c r="F33">
-        <v>1132.275</v>
+        <v>1168.8</v>
       </c>
       <c r="G33">
         <v>183.3</v>
@@ -4252,28 +4252,28 @@
         <v>360.85</v>
       </c>
       <c r="M33">
-        <v>62.6148075</v>
+        <v>64.63464</v>
       </c>
       <c r="N33">
-        <v>298.2351925</v>
+        <v>296.21536</v>
       </c>
       <c r="O33">
-        <v>89.47055775</v>
+        <v>88.86460799999999</v>
       </c>
       <c r="P33">
-        <v>208.76463475</v>
+        <v>207.350752</v>
       </c>
       <c r="Q33">
-        <v>304.6646347499999</v>
+        <v>303.250752</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08091647910034777</v>
+        <v>0.08131503827036923</v>
       </c>
       <c r="T33">
-        <v>0.8110041362666921</v>
+        <v>0.8202087360362408</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.763013804681903</v>
+        <v>5.582919623285593</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4298,22 +4298,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06768142602385108</v>
+        <v>0.06753038146846219</v>
       </c>
       <c r="C34">
-        <v>2192.331487538555</v>
+        <v>2177.895107788167</v>
       </c>
       <c r="D34">
-        <v>3177.831487538554</v>
+        <v>3199.920107788168</v>
       </c>
       <c r="E34">
-        <v>-444.4000000000001</v>
+        <v>-407.875</v>
       </c>
       <c r="F34">
-        <v>1168.8</v>
+        <v>1205.325</v>
       </c>
       <c r="G34">
         <v>183.3</v>
@@ -4334,28 +4334,28 @@
         <v>360.85</v>
       </c>
       <c r="M34">
-        <v>64.63464</v>
+        <v>66.65447250000001</v>
       </c>
       <c r="N34">
-        <v>296.21536</v>
+        <v>294.1955275</v>
       </c>
       <c r="O34">
-        <v>88.86460799999999</v>
+        <v>88.25865824999998</v>
       </c>
       <c r="P34">
-        <v>207.350752</v>
+        <v>205.93686925</v>
       </c>
       <c r="Q34">
-        <v>303.250752</v>
+        <v>301.8368692499999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08131503827036923</v>
+        <v>0.08172549472904805</v>
       </c>
       <c r="T34">
-        <v>0.8202087360362408</v>
+        <v>0.829688099978015</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.582919623285593</v>
+        <v>5.413740240761787</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4380,22 +4380,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06753038146846219</v>
+        <v>0.0673793369130733</v>
       </c>
       <c r="C35">
-        <v>2177.895107788167</v>
+        <v>2163.767946605357</v>
       </c>
       <c r="D35">
-        <v>3199.920107788168</v>
+        <v>3222.317946605357</v>
       </c>
       <c r="E35">
-        <v>-407.875</v>
+        <v>-371.3499999999999</v>
       </c>
       <c r="F35">
-        <v>1205.325</v>
+        <v>1241.85</v>
       </c>
       <c r="G35">
         <v>183.3</v>
@@ -4416,28 +4416,28 @@
         <v>360.85</v>
       </c>
       <c r="M35">
-        <v>66.65447250000001</v>
+        <v>68.674305</v>
       </c>
       <c r="N35">
-        <v>294.1955275</v>
+        <v>292.175695</v>
       </c>
       <c r="O35">
-        <v>88.25865824999998</v>
+        <v>87.65270849999999</v>
       </c>
       <c r="P35">
-        <v>205.93686925</v>
+        <v>204.5229865</v>
       </c>
       <c r="Q35">
-        <v>301.8368692499999</v>
+        <v>300.4229865</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08172549472904805</v>
+        <v>0.08214838926223228</v>
       </c>
       <c r="T35">
-        <v>0.829688099978015</v>
+        <v>0.8394547173725698</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.413740240761787</v>
+        <v>5.254512586621735</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4462,22 +4462,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0673793369130733</v>
+        <v>0.06722829235768442</v>
       </c>
       <c r="C36">
-        <v>2163.767946605357</v>
+        <v>2149.956542884626</v>
       </c>
       <c r="D36">
-        <v>3222.317946605357</v>
+        <v>3245.031542884626</v>
       </c>
       <c r="E36">
-        <v>-371.3499999999999</v>
+        <v>-334.8249999999998</v>
       </c>
       <c r="F36">
-        <v>1241.85</v>
+        <v>1278.375</v>
       </c>
       <c r="G36">
         <v>183.3</v>
@@ -4498,28 +4498,28 @@
         <v>360.85</v>
       </c>
       <c r="M36">
-        <v>68.674305</v>
+        <v>70.69413750000001</v>
       </c>
       <c r="N36">
-        <v>292.175695</v>
+        <v>290.1558625</v>
       </c>
       <c r="O36">
-        <v>87.65270849999999</v>
+        <v>87.04675874999998</v>
       </c>
       <c r="P36">
-        <v>204.5229865</v>
+        <v>203.10910375</v>
       </c>
       <c r="Q36">
-        <v>300.4229865</v>
+        <v>299.00910375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08214838926223228</v>
+        <v>0.0825842959348991</v>
       </c>
       <c r="T36">
-        <v>0.8394547173725698</v>
+        <v>0.8495218460715728</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.254512586621735</v>
+        <v>5.104383655575399</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4544,22 +4544,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06722829235768442</v>
+        <v>0.06707724780229553</v>
       </c>
       <c r="C37">
-        <v>2149.956542884626</v>
+        <v>2136.467621195706</v>
       </c>
       <c r="D37">
-        <v>3245.031542884626</v>
+        <v>3268.067621195706</v>
       </c>
       <c r="E37">
-        <v>-334.8249999999998</v>
+        <v>-298.3</v>
       </c>
       <c r="F37">
-        <v>1278.375</v>
+        <v>1314.9</v>
       </c>
       <c r="G37">
         <v>183.3</v>
@@ -4580,28 +4580,28 @@
         <v>360.85</v>
       </c>
       <c r="M37">
-        <v>70.69413750000001</v>
+        <v>72.71397</v>
       </c>
       <c r="N37">
-        <v>290.1558625</v>
+        <v>288.1360299999999</v>
       </c>
       <c r="O37">
-        <v>87.04675874999998</v>
+        <v>86.44080899999999</v>
       </c>
       <c r="P37">
-        <v>203.10910375</v>
+        <v>201.6952209999999</v>
       </c>
       <c r="Q37">
-        <v>299.00910375</v>
+        <v>297.5952209999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0825842959348991</v>
+        <v>0.08303382469108676</v>
       </c>
       <c r="T37">
-        <v>0.8495218460715728</v>
+        <v>0.8599035725424196</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.104383655575399</v>
+        <v>4.962595220698305</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4626,22 +4626,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06707724780229553</v>
+        <v>0.06692620324690664</v>
       </c>
       <c r="C38">
-        <v>2136.467621195706</v>
+        <v>2123.308098421086</v>
       </c>
       <c r="D38">
-        <v>3268.067621195706</v>
+        <v>3291.433098421086</v>
       </c>
       <c r="E38">
-        <v>-298.3000000000002</v>
+        <v>-261.7750000000001</v>
       </c>
       <c r="F38">
-        <v>1314.9</v>
+        <v>1351.425</v>
       </c>
       <c r="G38">
         <v>183.3</v>
@@ -4662,28 +4662,28 @@
         <v>360.85</v>
       </c>
       <c r="M38">
-        <v>72.71396999999999</v>
+        <v>74.7338025</v>
       </c>
       <c r="N38">
-        <v>288.13603</v>
+        <v>286.1161975</v>
       </c>
       <c r="O38">
-        <v>86.440809</v>
+        <v>85.83485924999999</v>
       </c>
       <c r="P38">
-        <v>201.695221</v>
+        <v>200.28133825</v>
       </c>
       <c r="Q38">
-        <v>297.595221</v>
+        <v>296.18133825</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08303382469108676</v>
+        <v>0.08349762420143911</v>
       </c>
       <c r="T38">
-        <v>0.8599035725424196</v>
+        <v>0.8706148776313882</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.962595220698306</v>
+        <v>4.828471025544298</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4708,22 +4708,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06692620324690664</v>
+        <v>0.06677515869151775</v>
       </c>
       <c r="C39">
-        <v>2123.308098421086</v>
+        <v>2110.485090680355</v>
       </c>
       <c r="D39">
-        <v>3291.433098421086</v>
+        <v>3315.135090680355</v>
       </c>
       <c r="E39">
-        <v>-261.7750000000001</v>
+        <v>-225.25</v>
       </c>
       <c r="F39">
-        <v>1351.425</v>
+        <v>1387.95</v>
       </c>
       <c r="G39">
         <v>183.3</v>
@@ -4744,28 +4744,28 @@
         <v>360.85</v>
       </c>
       <c r="M39">
-        <v>74.7338025</v>
+        <v>76.753635</v>
       </c>
       <c r="N39">
-        <v>286.1161975</v>
+        <v>284.096365</v>
       </c>
       <c r="O39">
-        <v>85.83485924999999</v>
+        <v>85.2289095</v>
       </c>
       <c r="P39">
-        <v>200.28133825</v>
+        <v>198.8674555</v>
       </c>
       <c r="Q39">
-        <v>296.18133825</v>
+        <v>294.7674555</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08349762420143911</v>
+        <v>0.08397638498631896</v>
       </c>
       <c r="T39">
-        <v>0.8706148776313882</v>
+        <v>0.8816717086909691</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.828471025544298</v>
+        <v>4.701405998556289</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4790,22 +4790,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06677515869151775</v>
+        <v>0.06662411413612886</v>
       </c>
       <c r="C40">
-        <v>2110.485090680355</v>
+        <v>2098.005920555882</v>
       </c>
       <c r="D40">
-        <v>3315.135090680355</v>
+        <v>3339.180920555882</v>
       </c>
       <c r="E40">
-        <v>-225.25</v>
+        <v>-188.7249999999999</v>
       </c>
       <c r="F40">
-        <v>1387.95</v>
+        <v>1424.475</v>
       </c>
       <c r="G40">
         <v>183.3</v>
@@ -4826,28 +4826,28 @@
         <v>360.85</v>
       </c>
       <c r="M40">
-        <v>76.753635</v>
+        <v>78.77346750000001</v>
       </c>
       <c r="N40">
-        <v>284.096365</v>
+        <v>282.0765325</v>
       </c>
       <c r="O40">
-        <v>85.2289095</v>
+        <v>84.62295974999999</v>
       </c>
       <c r="P40">
-        <v>198.8674555</v>
+        <v>197.45357275</v>
       </c>
       <c r="Q40">
-        <v>294.7674555</v>
+        <v>293.35357275</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08397638498631896</v>
+        <v>0.08447084284611289</v>
       </c>
       <c r="T40">
-        <v>0.8816717086909691</v>
+        <v>0.8930910588016836</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.701405998556289</v>
+        <v>4.580857126798436</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4872,22 +4872,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06662411413612886</v>
+        <v>0.06717306958073999</v>
       </c>
       <c r="C41">
-        <v>2098.005920555882</v>
+        <v>1975.715909594023</v>
       </c>
       <c r="D41">
-        <v>3339.180920555882</v>
+        <v>3253.415909594023</v>
       </c>
       <c r="E41">
-        <v>-188.7249999999999</v>
+        <v>-152.2</v>
       </c>
       <c r="F41">
-        <v>1424.475</v>
+        <v>1461</v>
       </c>
       <c r="G41">
         <v>183.3</v>
@@ -4908,45 +4908,45 @@
         <v>360.85</v>
       </c>
       <c r="M41">
-        <v>78.77346750000001</v>
+        <v>84.44580000000001</v>
       </c>
       <c r="N41">
-        <v>282.0765325</v>
+        <v>276.4041999999999</v>
       </c>
       <c r="O41">
-        <v>84.62295974999999</v>
+        <v>82.92125999999998</v>
       </c>
       <c r="P41">
-        <v>197.45357275</v>
+        <v>193.48294</v>
       </c>
       <c r="Q41">
-        <v>293.35357275</v>
+        <v>289.38294</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08447084284611289</v>
+        <v>0.08498178263456664</v>
       </c>
       <c r="T41">
-        <v>0.8930910588016836</v>
+        <v>0.9048910539160887</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.580857126798436</v>
+        <v>4.273155088826204</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4954,22 +4954,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06717306958073999</v>
+        <v>0.0670395250253511</v>
       </c>
       <c r="C42">
-        <v>1975.715909594023</v>
+        <v>1959.646921704617</v>
       </c>
       <c r="D42">
-        <v>3253.415909594023</v>
+        <v>3273.871921704617</v>
       </c>
       <c r="E42">
-        <v>-152.2</v>
+        <v>-115.675</v>
       </c>
       <c r="F42">
-        <v>1461</v>
+        <v>1497.525</v>
       </c>
       <c r="G42">
         <v>183.3</v>
@@ -4990,28 +4990,28 @@
         <v>360.85</v>
       </c>
       <c r="M42">
-        <v>84.44580000000001</v>
+        <v>86.55694500000001</v>
       </c>
       <c r="N42">
-        <v>276.4041999999999</v>
+        <v>274.293055</v>
       </c>
       <c r="O42">
-        <v>82.92125999999998</v>
+        <v>82.28791649999999</v>
       </c>
       <c r="P42">
-        <v>193.48294</v>
+        <v>192.0051385</v>
       </c>
       <c r="Q42">
-        <v>289.38294</v>
+        <v>287.9051385</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08498178263456664</v>
+        <v>0.08551004241584931</v>
       </c>
       <c r="T42">
-        <v>0.9048910539160887</v>
+        <v>0.9170910488648804</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.273155088826204</v>
+        <v>4.168931793976785</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5036,22 +5036,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0670395250253511</v>
+        <v>0.06690598046996221</v>
       </c>
       <c r="C43">
-        <v>1959.646921704617</v>
+        <v>1943.83679779419</v>
       </c>
       <c r="D43">
-        <v>3273.871921704617</v>
+        <v>3294.58679779419</v>
       </c>
       <c r="E43">
-        <v>-115.675</v>
+        <v>-79.14999999999986</v>
       </c>
       <c r="F43">
-        <v>1497.525</v>
+        <v>1534.05</v>
       </c>
       <c r="G43">
         <v>183.3</v>
@@ -5072,28 +5072,28 @@
         <v>360.85</v>
       </c>
       <c r="M43">
-        <v>86.55694500000001</v>
+        <v>88.66809000000002</v>
       </c>
       <c r="N43">
-        <v>274.293055</v>
+        <v>272.18191</v>
       </c>
       <c r="O43">
-        <v>82.28791649999999</v>
+        <v>81.65457299999998</v>
       </c>
       <c r="P43">
-        <v>192.0051385</v>
+        <v>190.527337</v>
       </c>
       <c r="Q43">
-        <v>287.9051385</v>
+        <v>286.427337</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08551004241584931</v>
+        <v>0.08605651805165898</v>
       </c>
       <c r="T43">
-        <v>0.9170910488648804</v>
+        <v>0.9297117332946648</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.168931793976785</v>
+        <v>4.069671513167814</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5118,22 +5118,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06690598046996221</v>
+        <v>0.06782593591457332</v>
       </c>
       <c r="C44">
-        <v>1943.83679779419</v>
+        <v>1769.707063351587</v>
       </c>
       <c r="D44">
-        <v>3294.58679779419</v>
+        <v>3156.982063351586</v>
       </c>
       <c r="E44">
-        <v>-79.15000000000009</v>
+        <v>-42.625</v>
       </c>
       <c r="F44">
-        <v>1534.05</v>
+        <v>1570.575</v>
       </c>
       <c r="G44">
         <v>183.3</v>
@@ -5154,45 +5154,45 @@
         <v>360.85</v>
       </c>
       <c r="M44">
-        <v>88.66809000000001</v>
+        <v>96.2762475</v>
       </c>
       <c r="N44">
-        <v>272.18191</v>
+        <v>264.5737525</v>
       </c>
       <c r="O44">
-        <v>81.65457299999998</v>
+        <v>79.37212574999998</v>
       </c>
       <c r="P44">
-        <v>190.527337</v>
+        <v>185.20162675</v>
       </c>
       <c r="Q44">
-        <v>286.427337</v>
+        <v>281.1016267499999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08605651805165898</v>
+        <v>0.08662216827118127</v>
       </c>
       <c r="T44">
-        <v>0.9297117332946646</v>
+        <v>0.9427752487570732</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.069671513167814</v>
+        <v>3.748068805859929</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5200,22 +5200,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06782593591457332</v>
+        <v>0.06771689135918443</v>
       </c>
       <c r="C45">
-        <v>1769.707063351587</v>
+        <v>1748.889204470604</v>
       </c>
       <c r="D45">
-        <v>3156.982063351586</v>
+        <v>3172.689204470604</v>
       </c>
       <c r="E45">
-        <v>-42.625</v>
+        <v>-6.100000000000136</v>
       </c>
       <c r="F45">
-        <v>1570.575</v>
+        <v>1607.1</v>
       </c>
       <c r="G45">
         <v>183.3</v>
@@ -5236,28 +5236,28 @@
         <v>360.85</v>
       </c>
       <c r="M45">
-        <v>96.2762475</v>
+        <v>98.51522999999999</v>
       </c>
       <c r="N45">
-        <v>264.5737525</v>
+        <v>262.33477</v>
       </c>
       <c r="O45">
-        <v>79.37212574999998</v>
+        <v>78.70043099999999</v>
       </c>
       <c r="P45">
-        <v>185.20162675</v>
+        <v>183.634339</v>
       </c>
       <c r="Q45">
-        <v>281.1016267499999</v>
+        <v>279.534339</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08662216827118127</v>
+        <v>0.08720802028425792</v>
       </c>
       <c r="T45">
-        <v>0.9427752487570732</v>
+        <v>0.956305318343139</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.748068805859929</v>
+        <v>3.662885423908568</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5282,22 +5282,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06771689135918443</v>
+        <v>0.06760784680379556</v>
       </c>
       <c r="C46">
-        <v>1748.889204470604</v>
+        <v>1728.228424666262</v>
       </c>
       <c r="D46">
-        <v>3172.689204470604</v>
+        <v>3188.553424666261</v>
       </c>
       <c r="E46">
-        <v>-6.100000000000136</v>
+        <v>30.42499999999995</v>
       </c>
       <c r="F46">
-        <v>1607.1</v>
+        <v>1643.625</v>
       </c>
       <c r="G46">
         <v>183.3</v>
@@ -5318,28 +5318,28 @@
         <v>360.85</v>
       </c>
       <c r="M46">
-        <v>98.51522999999999</v>
+        <v>100.7542125</v>
       </c>
       <c r="N46">
-        <v>262.33477</v>
+        <v>260.0957875</v>
       </c>
       <c r="O46">
-        <v>78.70043099999999</v>
+        <v>78.02873624999999</v>
       </c>
       <c r="P46">
-        <v>183.634339</v>
+        <v>182.06705125</v>
       </c>
       <c r="Q46">
-        <v>279.534339</v>
+        <v>277.9670512499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08720802028425792</v>
+        <v>0.087815176006901</v>
       </c>
       <c r="T46">
-        <v>0.956305318343139</v>
+        <v>0.9703273904596075</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.662885423908568</v>
+        <v>3.581487970043932</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5364,22 +5364,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06760784680379556</v>
+        <v>0.06749880224840665</v>
       </c>
       <c r="C47">
-        <v>1728.228424666262</v>
+        <v>1707.727092080993</v>
       </c>
       <c r="D47">
-        <v>3188.553424666261</v>
+        <v>3204.577092080993</v>
       </c>
       <c r="E47">
-        <v>30.42499999999995</v>
+        <v>66.95000000000005</v>
       </c>
       <c r="F47">
-        <v>1643.625</v>
+        <v>1680.15</v>
       </c>
       <c r="G47">
         <v>183.3</v>
@@ -5400,28 +5400,28 @@
         <v>360.85</v>
       </c>
       <c r="M47">
-        <v>100.7542125</v>
+        <v>102.993195</v>
       </c>
       <c r="N47">
-        <v>260.0957875</v>
+        <v>257.856805</v>
       </c>
       <c r="O47">
-        <v>78.02873624999999</v>
+        <v>77.35704149999998</v>
       </c>
       <c r="P47">
-        <v>182.06705125</v>
+        <v>180.4997635</v>
       </c>
       <c r="Q47">
-        <v>277.9670512499999</v>
+        <v>276.3997634999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.087815176006901</v>
+        <v>0.08844481897853085</v>
       </c>
       <c r="T47">
-        <v>0.9703273904596075</v>
+        <v>0.9848687985803893</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5438,7 +5438,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.581487970043932</v>
+        <v>3.503629535912542</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5446,22 +5446,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06749880224840665</v>
+        <v>0.06831095769301779</v>
       </c>
       <c r="C48">
-        <v>1707.727092080993</v>
+        <v>1555.586631890379</v>
       </c>
       <c r="D48">
-        <v>3204.577092080993</v>
+        <v>3088.961631890379</v>
       </c>
       <c r="E48">
-        <v>66.95000000000005</v>
+        <v>103.4750000000001</v>
       </c>
       <c r="F48">
-        <v>1680.15</v>
+        <v>1716.675</v>
       </c>
       <c r="G48">
         <v>183.3</v>
@@ -5482,45 +5482,45 @@
         <v>360.85</v>
       </c>
       <c r="M48">
-        <v>102.993195</v>
+        <v>110.0388675</v>
       </c>
       <c r="N48">
-        <v>257.856805</v>
+        <v>250.8111324999999</v>
       </c>
       <c r="O48">
-        <v>77.35704149999998</v>
+        <v>75.24333974999998</v>
       </c>
       <c r="P48">
-        <v>180.4997635</v>
+        <v>175.56779275</v>
       </c>
       <c r="Q48">
-        <v>276.3997634999999</v>
+        <v>271.4677927499999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08844481897853085</v>
+        <v>0.0890982220622977</v>
       </c>
       <c r="T48">
-        <v>0.9848687985803893</v>
+        <v>0.9999589390830876</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.503629535912542</v>
+        <v>3.279295836082645</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5528,22 +5528,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06831095769301779</v>
+        <v>0.06822151313762889</v>
       </c>
       <c r="C49">
-        <v>1555.586631890379</v>
+        <v>1531.384207895034</v>
       </c>
       <c r="D49">
-        <v>3088.961631890379</v>
+        <v>3101.284207895033</v>
       </c>
       <c r="E49">
-        <v>103.4750000000001</v>
+        <v>140</v>
       </c>
       <c r="F49">
-        <v>1716.675</v>
+        <v>1753.2</v>
       </c>
       <c r="G49">
         <v>183.3</v>
@@ -5564,28 +5564,28 @@
         <v>360.85</v>
       </c>
       <c r="M49">
-        <v>110.0388675</v>
+        <v>112.38012</v>
       </c>
       <c r="N49">
-        <v>250.8111324999999</v>
+        <v>248.46988</v>
       </c>
       <c r="O49">
-        <v>75.24333974999998</v>
+        <v>74.54096399999999</v>
       </c>
       <c r="P49">
-        <v>175.56779275</v>
+        <v>173.928916</v>
       </c>
       <c r="Q49">
-        <v>271.4677927499999</v>
+        <v>269.8289159999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.0890982220622977</v>
+        <v>0.08977675603390171</v>
       </c>
       <c r="T49">
-        <v>0.9999589390830876</v>
+        <v>1.01562946960512</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.279295836082645</v>
+        <v>3.210977172830924</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5610,22 +5610,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06822151313762889</v>
+        <v>0.06813206858224</v>
       </c>
       <c r="C50">
-        <v>1531.384207895034</v>
+        <v>1507.280492832802</v>
       </c>
       <c r="D50">
-        <v>3101.284207895033</v>
+        <v>3113.705492832802</v>
       </c>
       <c r="E50">
-        <v>140</v>
+        <v>176.5249999999999</v>
       </c>
       <c r="F50">
-        <v>1753.2</v>
+        <v>1789.725</v>
       </c>
       <c r="G50">
         <v>183.3</v>
@@ -5646,28 +5646,28 @@
         <v>360.85</v>
       </c>
       <c r="M50">
-        <v>112.38012</v>
+        <v>114.7213725</v>
       </c>
       <c r="N50">
-        <v>248.46988</v>
+        <v>246.1286275</v>
       </c>
       <c r="O50">
-        <v>74.54096399999999</v>
+        <v>73.83858824999999</v>
       </c>
       <c r="P50">
-        <v>173.928916</v>
+        <v>172.29003925</v>
       </c>
       <c r="Q50">
-        <v>269.8289159999999</v>
+        <v>268.1900392499999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08977675603390171</v>
+        <v>0.09048189918086275</v>
       </c>
       <c r="T50">
-        <v>1.01562946960512</v>
+        <v>1.03191453073586</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.210977172830924</v>
+        <v>3.145447026446619</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5692,22 +5692,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06813206858224</v>
+        <v>0.06804262402685111</v>
       </c>
       <c r="C51">
-        <v>1507.280492832802</v>
+        <v>1483.276677522258</v>
       </c>
       <c r="D51">
-        <v>3113.705492832802</v>
+        <v>3126.226677522258</v>
       </c>
       <c r="E51">
-        <v>176.5249999999999</v>
+        <v>213.05</v>
       </c>
       <c r="F51">
-        <v>1789.725</v>
+        <v>1826.25</v>
       </c>
       <c r="G51">
         <v>183.3</v>
@@ -5728,28 +5728,28 @@
         <v>360.85</v>
       </c>
       <c r="M51">
-        <v>114.7213725</v>
+        <v>117.062625</v>
       </c>
       <c r="N51">
-        <v>246.1286275</v>
+        <v>243.7873749999999</v>
       </c>
       <c r="O51">
-        <v>73.83858824999999</v>
+        <v>73.13621249999998</v>
       </c>
       <c r="P51">
-        <v>172.29003925</v>
+        <v>170.6511624999999</v>
       </c>
       <c r="Q51">
-        <v>268.1900392499999</v>
+        <v>266.5511624999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09048189918086275</v>
+        <v>0.09121524805370224</v>
       </c>
       <c r="T51">
-        <v>1.03191453073586</v>
+        <v>1.04885099431183</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.145447026446619</v>
+        <v>3.082538085917686</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5774,22 +5774,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06804262402685111</v>
+        <v>0.06795317947146223</v>
       </c>
       <c r="C52">
-        <v>1483.276677522258</v>
+        <v>1459.373972013938</v>
       </c>
       <c r="D52">
-        <v>3126.226677522258</v>
+        <v>3138.848972013938</v>
       </c>
       <c r="E52">
-        <v>213.05</v>
+        <v>249.575</v>
       </c>
       <c r="F52">
-        <v>1826.25</v>
+        <v>1862.775</v>
       </c>
       <c r="G52">
         <v>183.3</v>
@@ -5810,28 +5810,28 @@
         <v>360.85</v>
       </c>
       <c r="M52">
-        <v>117.062625</v>
+        <v>119.4038775</v>
       </c>
       <c r="N52">
-        <v>243.7873749999999</v>
+        <v>241.4461224999999</v>
       </c>
       <c r="O52">
-        <v>73.13621249999998</v>
+        <v>72.43383674999998</v>
       </c>
       <c r="P52">
-        <v>170.6511624999999</v>
+        <v>169.01228575</v>
       </c>
       <c r="Q52">
-        <v>266.5511624999999</v>
+        <v>264.9122857499999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09121524805370224</v>
+        <v>0.09197852953359639</v>
       </c>
       <c r="T52">
-        <v>1.04885099431183</v>
+        <v>1.06647874211539</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.082538085917686</v>
+        <v>3.022096162664399</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5856,22 +5856,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06795317947146223</v>
+        <v>0.07070293491607335</v>
       </c>
       <c r="C53">
-        <v>1459.373972013938</v>
+        <v>1076.260624909658</v>
       </c>
       <c r="D53">
-        <v>3138.848972013938</v>
+        <v>2792.260624909658</v>
       </c>
       <c r="E53">
-        <v>249.575</v>
+        <v>286.0999999999999</v>
       </c>
       <c r="F53">
-        <v>1862.775</v>
+        <v>1899.3</v>
       </c>
       <c r="G53">
         <v>183.3</v>
@@ -5892,45 +5892,45 @@
         <v>360.85</v>
       </c>
       <c r="M53">
-        <v>119.4038775</v>
+        <v>136.55967</v>
       </c>
       <c r="N53">
-        <v>241.4461224999999</v>
+        <v>224.29033</v>
       </c>
       <c r="O53">
-        <v>72.43383674999998</v>
+        <v>67.28709899999998</v>
       </c>
       <c r="P53">
-        <v>169.01228575</v>
+        <v>157.003231</v>
       </c>
       <c r="Q53">
-        <v>264.9122857499999</v>
+        <v>252.9032309999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09197852953359639</v>
+        <v>0.09277361440848614</v>
       </c>
       <c r="T53">
-        <v>1.06647874211539</v>
+        <v>1.084840979410765</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.022096162664399</v>
+        <v>2.642434622169195</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5938,22 +5938,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07070293491607335</v>
+        <v>0.07066809036068446</v>
       </c>
       <c r="C54">
-        <v>1076.260624909658</v>
+        <v>1043.648071687586</v>
       </c>
       <c r="D54">
-        <v>2792.260624909658</v>
+        <v>2796.173071687586</v>
       </c>
       <c r="E54">
-        <v>286.0999999999999</v>
+        <v>322.625</v>
       </c>
       <c r="F54">
-        <v>1899.3</v>
+        <v>1935.825</v>
       </c>
       <c r="G54">
         <v>183.3</v>
@@ -5974,28 +5974,28 @@
         <v>360.85</v>
       </c>
       <c r="M54">
-        <v>136.55967</v>
+        <v>139.1858175</v>
       </c>
       <c r="N54">
-        <v>224.29033</v>
+        <v>221.6641825</v>
       </c>
       <c r="O54">
-        <v>67.28709899999998</v>
+        <v>66.49925474999998</v>
       </c>
       <c r="P54">
-        <v>157.003231</v>
+        <v>155.16492775</v>
       </c>
       <c r="Q54">
-        <v>252.9032309999999</v>
+        <v>251.06492775</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09277361440848614</v>
+        <v>0.09360253268230737</v>
       </c>
       <c r="T54">
-        <v>1.084840979410765</v>
+        <v>1.103984588505944</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.642434622169195</v>
+        <v>2.592577365147135</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6020,22 +6020,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07066809036068446</v>
+        <v>0.07063324580529558</v>
       </c>
       <c r="C55">
-        <v>1043.648071687586</v>
+        <v>1011.046497897644</v>
       </c>
       <c r="D55">
-        <v>2796.173071687586</v>
+        <v>2800.096497897644</v>
       </c>
       <c r="E55">
-        <v>322.625</v>
+        <v>359.1500000000001</v>
       </c>
       <c r="F55">
-        <v>1935.825</v>
+        <v>1972.35</v>
       </c>
       <c r="G55">
         <v>183.3</v>
@@ -6056,28 +6056,28 @@
         <v>360.85</v>
       </c>
       <c r="M55">
-        <v>139.1858175</v>
+        <v>141.811965</v>
       </c>
       <c r="N55">
-        <v>221.6641825</v>
+        <v>219.038035</v>
       </c>
       <c r="O55">
-        <v>66.49925474999998</v>
+        <v>65.71141049999999</v>
       </c>
       <c r="P55">
-        <v>155.16492775</v>
+        <v>153.3266245</v>
       </c>
       <c r="Q55">
-        <v>251.06492775</v>
+        <v>249.2266245</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09360253268230737</v>
+        <v>0.09446749088107734</v>
       </c>
       <c r="T55">
-        <v>1.103984588505944</v>
+        <v>1.123960528431347</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.592577365147135</v>
+        <v>2.544566673199966</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6102,22 +6102,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07063324580529558</v>
+        <v>0.07209990124990669</v>
       </c>
       <c r="C56">
-        <v>1011.046497897644</v>
+        <v>818.3697034458435</v>
       </c>
       <c r="D56">
-        <v>2800.096497897644</v>
+        <v>2643.944703445844</v>
       </c>
       <c r="E56">
-        <v>359.1500000000001</v>
+        <v>395.6750000000002</v>
       </c>
       <c r="F56">
-        <v>1972.35</v>
+        <v>2008.875</v>
       </c>
       <c r="G56">
         <v>183.3</v>
@@ -6138,45 +6138,45 @@
         <v>360.85</v>
       </c>
       <c r="M56">
-        <v>141.811965</v>
+        <v>152.272725</v>
       </c>
       <c r="N56">
-        <v>219.038035</v>
+        <v>208.5772749999999</v>
       </c>
       <c r="O56">
-        <v>65.71141049999999</v>
+        <v>62.57318249999997</v>
       </c>
       <c r="P56">
-        <v>153.3266245</v>
+        <v>146.0040925</v>
       </c>
       <c r="Q56">
-        <v>249.2266245</v>
+        <v>241.9040924999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09446749088107734</v>
+        <v>0.0953708916664593</v>
       </c>
       <c r="T56">
-        <v>1.123960528431347</v>
+        <v>1.144824287908991</v>
       </c>
       <c r="U56">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.544566673199966</v>
+        <v>2.369761229399421</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6184,22 +6184,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07209990124990669</v>
+        <v>0.0720923566945178</v>
       </c>
       <c r="C57">
-        <v>818.3697034458435</v>
+        <v>782.6033797216933</v>
       </c>
       <c r="D57">
-        <v>2643.944703445844</v>
+        <v>2644.703379721693</v>
       </c>
       <c r="E57">
-        <v>395.6750000000002</v>
+        <v>432.2</v>
       </c>
       <c r="F57">
-        <v>2008.875</v>
+        <v>2045.4</v>
       </c>
       <c r="G57">
         <v>183.3</v>
@@ -6220,28 +6220,28 @@
         <v>360.85</v>
       </c>
       <c r="M57">
-        <v>152.272725</v>
+        <v>155.04132</v>
       </c>
       <c r="N57">
-        <v>208.5772749999999</v>
+        <v>205.80868</v>
       </c>
       <c r="O57">
-        <v>62.57318249999997</v>
+        <v>61.74260399999999</v>
       </c>
       <c r="P57">
-        <v>146.0040925</v>
+        <v>144.066076</v>
       </c>
       <c r="Q57">
-        <v>241.9040924999999</v>
+        <v>239.9660759999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.0953708916664593</v>
+        <v>0.0963153561239041</v>
       </c>
       <c r="T57">
-        <v>1.144824287908991</v>
+        <v>1.166636400090164</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.369761229399421</v>
+        <v>2.327444064588717</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6266,22 +6266,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0720923566945178</v>
+        <v>0.07208481213912891</v>
       </c>
       <c r="C58">
-        <v>782.6033797216933</v>
+        <v>746.8374915247323</v>
       </c>
       <c r="D58">
-        <v>2644.703379721693</v>
+        <v>2645.462491524732</v>
       </c>
       <c r="E58">
-        <v>432.2</v>
+        <v>468.7250000000001</v>
       </c>
       <c r="F58">
-        <v>2045.4</v>
+        <v>2081.925</v>
       </c>
       <c r="G58">
         <v>183.3</v>
@@ -6302,28 +6302,28 @@
         <v>360.85</v>
       </c>
       <c r="M58">
-        <v>155.04132</v>
+        <v>157.809915</v>
       </c>
       <c r="N58">
-        <v>205.80868</v>
+        <v>203.0400849999999</v>
       </c>
       <c r="O58">
-        <v>61.74260399999999</v>
+        <v>60.91202549999998</v>
       </c>
       <c r="P58">
-        <v>144.066076</v>
+        <v>142.1280594999999</v>
       </c>
       <c r="Q58">
-        <v>239.9660759999999</v>
+        <v>238.0280594999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.0963153561239041</v>
+        <v>0.09730374916076492</v>
       </c>
       <c r="T58">
-        <v>1.166636400090164</v>
+        <v>1.189463029116973</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.327444064588717</v>
+        <v>2.286611712578388</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6348,22 +6348,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07208481213912891</v>
+        <v>0.07207726758374003</v>
       </c>
       <c r="C59">
-        <v>746.8374915247323</v>
+        <v>711.0720392300987</v>
       </c>
       <c r="D59">
-        <v>2645.462491524732</v>
+        <v>2646.222039230099</v>
       </c>
       <c r="E59">
-        <v>468.7250000000001</v>
+        <v>505.2500000000002</v>
       </c>
       <c r="F59">
-        <v>2081.925</v>
+        <v>2118.45</v>
       </c>
       <c r="G59">
         <v>183.3</v>
@@ -6384,28 +6384,28 @@
         <v>360.85</v>
       </c>
       <c r="M59">
-        <v>157.809915</v>
+        <v>160.57851</v>
       </c>
       <c r="N59">
-        <v>203.0400849999999</v>
+        <v>200.2714899999999</v>
       </c>
       <c r="O59">
-        <v>60.91202549999998</v>
+        <v>60.08144699999998</v>
       </c>
       <c r="P59">
-        <v>142.1280594999999</v>
+        <v>140.1900429999999</v>
       </c>
       <c r="Q59">
-        <v>238.0280594999999</v>
+        <v>236.0900429999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09730374916076492</v>
+        <v>0.09833920853271436</v>
       </c>
       <c r="T59">
-        <v>1.189463029116973</v>
+        <v>1.213376640478392</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.286611712578388</v>
+        <v>2.247187372706347</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6430,22 +6430,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07207726758374003</v>
+        <v>0.07206972302835113</v>
       </c>
       <c r="C60">
-        <v>711.0720392300991</v>
+        <v>675.3070232133618</v>
       </c>
       <c r="D60">
-        <v>2646.222039230099</v>
+        <v>2646.982023213362</v>
       </c>
       <c r="E60">
-        <v>505.2499999999998</v>
+        <v>541.7749999999999</v>
       </c>
       <c r="F60">
-        <v>2118.45</v>
+        <v>2154.975</v>
       </c>
       <c r="G60">
         <v>183.3</v>
@@ -6466,28 +6466,28 @@
         <v>360.85</v>
       </c>
       <c r="M60">
-        <v>160.57851</v>
+        <v>163.347105</v>
       </c>
       <c r="N60">
-        <v>200.27149</v>
+        <v>197.502895</v>
       </c>
       <c r="O60">
-        <v>60.08144699999999</v>
+        <v>59.25086849999999</v>
       </c>
       <c r="P60">
-        <v>140.190043</v>
+        <v>138.2520265</v>
       </c>
       <c r="Q60">
-        <v>236.090043</v>
+        <v>234.1520264999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09833920853271436</v>
+        <v>0.0994251781179296</v>
       </c>
       <c r="T60">
-        <v>1.213376640478391</v>
+        <v>1.238456769467196</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.247187372706348</v>
+        <v>2.209099451135054</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6512,22 +6512,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07206972302835113</v>
+        <v>0.07206217847296226</v>
       </c>
       <c r="C61">
-        <v>675.3070232133618</v>
+        <v>639.5424438505165</v>
       </c>
       <c r="D61">
-        <v>2646.982023213362</v>
+        <v>2647.742443850516</v>
       </c>
       <c r="E61">
-        <v>541.7749999999999</v>
+        <v>578.3</v>
       </c>
       <c r="F61">
-        <v>2154.975</v>
+        <v>2191.5</v>
       </c>
       <c r="G61">
         <v>183.3</v>
@@ -6548,28 +6548,28 @@
         <v>360.85</v>
       </c>
       <c r="M61">
-        <v>163.347105</v>
+        <v>166.1157</v>
       </c>
       <c r="N61">
-        <v>197.502895</v>
+        <v>194.7343</v>
       </c>
       <c r="O61">
-        <v>59.25086849999999</v>
+        <v>58.42028999999999</v>
       </c>
       <c r="P61">
-        <v>138.2520265</v>
+        <v>136.31401</v>
       </c>
       <c r="Q61">
-        <v>234.1520264999999</v>
+        <v>232.2140099999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.0994251781179296</v>
+        <v>0.1005654461824056</v>
       </c>
       <c r="T61">
-        <v>1.238456769467196</v>
+        <v>1.264790904905442</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6586,7 +6586,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.209099451135054</v>
+        <v>2.17228112694947</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6594,22 +6594,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07206217847296226</v>
+        <v>0.07205463391757337</v>
       </c>
       <c r="C62">
-        <v>639.5424438505165</v>
+        <v>603.7783015179994</v>
       </c>
       <c r="D62">
-        <v>2647.742443850516</v>
+        <v>2648.503301517999</v>
       </c>
       <c r="E62">
-        <v>578.3</v>
+        <v>614.825</v>
       </c>
       <c r="F62">
-        <v>2191.5</v>
+        <v>2228.025</v>
       </c>
       <c r="G62">
         <v>183.3</v>
@@ -6630,28 +6630,28 @@
         <v>360.85</v>
       </c>
       <c r="M62">
-        <v>166.1157</v>
+        <v>168.884295</v>
       </c>
       <c r="N62">
-        <v>194.7343</v>
+        <v>191.965705</v>
       </c>
       <c r="O62">
-        <v>58.42028999999999</v>
+        <v>57.58971149999999</v>
       </c>
       <c r="P62">
-        <v>136.31401</v>
+        <v>134.3759935</v>
       </c>
       <c r="Q62">
-        <v>232.2140099999999</v>
+        <v>230.2759934999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1005654461824056</v>
+        <v>0.1017641895322394</v>
       </c>
       <c r="T62">
-        <v>1.264790904905442</v>
+        <v>1.2924755088277</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.17228112694947</v>
+        <v>2.136669960933904</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6676,22 +6676,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07205463391757337</v>
+        <v>0.07204708936218449</v>
       </c>
       <c r="C63">
-        <v>603.7783015179994</v>
+        <v>568.0145965926727</v>
       </c>
       <c r="D63">
-        <v>2648.503301517999</v>
+        <v>2649.264596592673</v>
       </c>
       <c r="E63">
-        <v>614.825</v>
+        <v>651.3500000000001</v>
       </c>
       <c r="F63">
-        <v>2228.025</v>
+        <v>2264.55</v>
       </c>
       <c r="G63">
         <v>183.3</v>
@@ -6712,28 +6712,28 @@
         <v>360.85</v>
       </c>
       <c r="M63">
-        <v>168.884295</v>
+        <v>171.65289</v>
       </c>
       <c r="N63">
-        <v>191.965705</v>
+        <v>189.1971099999999</v>
       </c>
       <c r="O63">
-        <v>57.58971149999999</v>
+        <v>56.75913299999998</v>
       </c>
       <c r="P63">
-        <v>134.3759935</v>
+        <v>132.4379769999999</v>
       </c>
       <c r="Q63">
-        <v>230.2759934999999</v>
+        <v>228.3379769999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1017641895322394</v>
+        <v>0.1030260246373276</v>
       </c>
       <c r="T63">
-        <v>1.2924755088277</v>
+        <v>1.321617197166919</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.136669960933904</v>
+        <v>2.102207542209163</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6758,22 +6758,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07204708936218449</v>
+        <v>0.0720395448067956</v>
       </c>
       <c r="C64">
-        <v>568.0145965926727</v>
+        <v>532.2513294518358</v>
       </c>
       <c r="D64">
-        <v>2649.264596592673</v>
+        <v>2650.026329451835</v>
       </c>
       <c r="E64">
-        <v>651.3500000000001</v>
+        <v>687.8749999999998</v>
       </c>
       <c r="F64">
-        <v>2264.55</v>
+        <v>2301.075</v>
       </c>
       <c r="G64">
         <v>183.3</v>
@@ -6794,28 +6794,28 @@
         <v>360.85</v>
       </c>
       <c r="M64">
-        <v>171.65289</v>
+        <v>174.421485</v>
       </c>
       <c r="N64">
-        <v>189.1971099999999</v>
+        <v>186.428515</v>
       </c>
       <c r="O64">
-        <v>56.75913299999998</v>
+        <v>55.92855449999999</v>
       </c>
       <c r="P64">
-        <v>132.4379769999999</v>
+        <v>130.4999605</v>
       </c>
       <c r="Q64">
-        <v>228.3379769999999</v>
+        <v>226.3999605</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1030260246373276</v>
+        <v>0.1043560670453935</v>
       </c>
       <c r="T64">
-        <v>1.321617197166919</v>
+        <v>1.352334111902852</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.102207542209163</v>
+        <v>2.068839168523304</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6840,22 +6840,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0720395448067956</v>
+        <v>0.07203200025140671</v>
       </c>
       <c r="C65">
-        <v>532.2513294518358</v>
+        <v>496.4885004732191</v>
       </c>
       <c r="D65">
-        <v>2650.026329451835</v>
+        <v>2650.788500473219</v>
       </c>
       <c r="E65">
-        <v>687.8749999999998</v>
+        <v>724.3999999999999</v>
       </c>
       <c r="F65">
-        <v>2301.075</v>
+        <v>2337.6</v>
       </c>
       <c r="G65">
         <v>183.3</v>
@@ -6876,28 +6876,28 @@
         <v>360.85</v>
       </c>
       <c r="M65">
-        <v>174.421485</v>
+        <v>177.19008</v>
       </c>
       <c r="N65">
-        <v>186.428515</v>
+        <v>183.65992</v>
       </c>
       <c r="O65">
-        <v>55.92855449999999</v>
+        <v>55.09797599999999</v>
       </c>
       <c r="P65">
-        <v>130.4999605</v>
+        <v>128.561944</v>
       </c>
       <c r="Q65">
-        <v>226.3999605</v>
+        <v>224.461944</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1043560670453935</v>
+        <v>0.105760000698352</v>
       </c>
       <c r="T65">
-        <v>1.352334111902852</v>
+        <v>1.384757521901893</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.068839168523304</v>
+        <v>2.036513556515128</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6922,22 +6922,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07203200025140671</v>
+        <v>0.07202445569601783</v>
       </c>
       <c r="C66">
-        <v>496.4885004732191</v>
+        <v>460.7261100349915</v>
       </c>
       <c r="D66">
-        <v>2650.788500473219</v>
+        <v>2651.551110034991</v>
       </c>
       <c r="E66">
-        <v>724.3999999999999</v>
+        <v>760.925</v>
       </c>
       <c r="F66">
-        <v>2337.6</v>
+        <v>2374.125</v>
       </c>
       <c r="G66">
         <v>183.3</v>
@@ -6958,28 +6958,28 @@
         <v>360.85</v>
       </c>
       <c r="M66">
-        <v>177.19008</v>
+        <v>179.958675</v>
       </c>
       <c r="N66">
-        <v>183.65992</v>
+        <v>180.8913249999999</v>
       </c>
       <c r="O66">
-        <v>55.09797599999999</v>
+        <v>54.26739749999998</v>
       </c>
       <c r="P66">
-        <v>128.561944</v>
+        <v>126.6239275</v>
       </c>
       <c r="Q66">
-        <v>224.461944</v>
+        <v>222.5239274999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.105760000698352</v>
+        <v>0.1072441591314795</v>
       </c>
       <c r="T66">
-        <v>1.384757521901893</v>
+        <v>1.419033698186593</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.036513556515128</v>
+        <v>2.005182578722587</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7004,22 +7004,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07202445569601783</v>
+        <v>0.07857731114062894</v>
       </c>
       <c r="C67">
-        <v>460.7261100349915</v>
+        <v>-105.8982337919056</v>
       </c>
       <c r="D67">
-        <v>2651.551110034991</v>
+        <v>2121.451766208094</v>
       </c>
       <c r="E67">
-        <v>760.925</v>
+        <v>797.45</v>
       </c>
       <c r="F67">
-        <v>2374.125</v>
+        <v>2410.65</v>
       </c>
       <c r="G67">
         <v>183.3</v>
@@ -7040,45 +7040,45 @@
         <v>360.85</v>
       </c>
       <c r="M67">
-        <v>179.958675</v>
+        <v>216.9585</v>
       </c>
       <c r="N67">
-        <v>180.8913249999999</v>
+        <v>143.8915</v>
       </c>
       <c r="O67">
-        <v>54.26739749999998</v>
+        <v>43.16745</v>
       </c>
       <c r="P67">
-        <v>126.6239275</v>
+        <v>100.72405</v>
       </c>
       <c r="Q67">
-        <v>222.5239274999999</v>
+        <v>196.62405</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1072441591314795</v>
+        <v>0.1088156210018498</v>
       </c>
       <c r="T67">
-        <v>1.419033698186593</v>
+        <v>1.4553261201351</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.3</v>
       </c>
       <c r="W67">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.005182578722587</v>
+        <v>1.663221307300705</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7086,22 +7086,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07857731114062894</v>
+        <v>0.07866916658524006</v>
       </c>
       <c r="C68">
-        <v>-105.8982337919056</v>
+        <v>-148.3517958897842</v>
       </c>
       <c r="D68">
-        <v>2121.451766208094</v>
+        <v>2115.523204110216</v>
       </c>
       <c r="E68">
-        <v>797.45</v>
+        <v>833.9750000000001</v>
       </c>
       <c r="F68">
-        <v>2410.65</v>
+        <v>2447.175</v>
       </c>
       <c r="G68">
         <v>183.3</v>
@@ -7122,28 +7122,28 @@
         <v>360.85</v>
       </c>
       <c r="M68">
-        <v>216.9585</v>
+        <v>220.24575</v>
       </c>
       <c r="N68">
-        <v>143.8915</v>
+        <v>140.60425</v>
       </c>
       <c r="O68">
-        <v>43.16745</v>
+        <v>42.18127499999999</v>
       </c>
       <c r="P68">
-        <v>100.72405</v>
+        <v>98.42297499999997</v>
       </c>
       <c r="Q68">
-        <v>196.62405</v>
+        <v>194.3229749999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1088156210018498</v>
+        <v>0.1104823229855759</v>
       </c>
       <c r="T68">
-        <v>1.4553261201351</v>
+        <v>1.493818082807758</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.663221307300705</v>
+        <v>1.638397108684276</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7168,22 +7168,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07866916658524006</v>
+        <v>0.07876102202985116</v>
       </c>
       <c r="C69">
-        <v>-148.3517958897842</v>
+        <v>-190.7723146732324</v>
       </c>
       <c r="D69">
-        <v>2115.523204110216</v>
+        <v>2109.627685326768</v>
       </c>
       <c r="E69">
-        <v>833.9750000000001</v>
+        <v>870.5000000000002</v>
       </c>
       <c r="F69">
-        <v>2447.175</v>
+        <v>2483.7</v>
       </c>
       <c r="G69">
         <v>183.3</v>
@@ -7204,28 +7204,28 @@
         <v>360.85</v>
       </c>
       <c r="M69">
-        <v>220.24575</v>
+        <v>223.533</v>
       </c>
       <c r="N69">
-        <v>140.60425</v>
+        <v>137.317</v>
       </c>
       <c r="O69">
-        <v>42.18127499999999</v>
+        <v>41.19509999999998</v>
       </c>
       <c r="P69">
-        <v>98.42297499999997</v>
+        <v>96.12189999999997</v>
       </c>
       <c r="Q69">
-        <v>194.3229749999999</v>
+        <v>192.0219</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1104823229855759</v>
+        <v>0.1122531938432849</v>
       </c>
       <c r="T69">
-        <v>1.493818082807758</v>
+        <v>1.534715793147457</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.638397108684276</v>
+        <v>1.614303033556566</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7250,22 +7250,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07876102202985116</v>
+        <v>0.07885287747446228</v>
       </c>
       <c r="C70">
-        <v>-190.7723146732324</v>
+        <v>-233.1600656288583</v>
       </c>
       <c r="D70">
-        <v>2109.627685326768</v>
+        <v>2103.764934371142</v>
       </c>
       <c r="E70">
-        <v>870.5000000000002</v>
+        <v>907.0250000000003</v>
       </c>
       <c r="F70">
-        <v>2483.7</v>
+        <v>2520.225</v>
       </c>
       <c r="G70">
         <v>183.3</v>
@@ -7286,28 +7286,28 @@
         <v>360.85</v>
       </c>
       <c r="M70">
-        <v>223.533</v>
+        <v>226.82025</v>
       </c>
       <c r="N70">
-        <v>137.317</v>
+        <v>134.02975</v>
       </c>
       <c r="O70">
-        <v>41.19509999999998</v>
+        <v>40.20892499999999</v>
       </c>
       <c r="P70">
-        <v>96.12189999999997</v>
+        <v>93.82082499999996</v>
       </c>
       <c r="Q70">
-        <v>192.0219</v>
+        <v>189.7208249999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1122531938432849</v>
+        <v>0.1141383144337493</v>
       </c>
       <c r="T70">
-        <v>1.534715793147457</v>
+        <v>1.578252065444557</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.614303033556566</v>
+        <v>1.590907337418065</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7332,22 +7332,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07885287747446228</v>
+        <v>0.07894473291907339</v>
       </c>
       <c r="C71">
-        <v>-233.1600656288583</v>
+        <v>-275.5153211893958</v>
       </c>
       <c r="D71">
-        <v>2103.764934371142</v>
+        <v>2097.934678810605</v>
       </c>
       <c r="E71">
-        <v>907.0250000000003</v>
+        <v>943.5500000000004</v>
       </c>
       <c r="F71">
-        <v>2520.225</v>
+        <v>2556.75</v>
       </c>
       <c r="G71">
         <v>183.3</v>
@@ -7368,28 +7368,28 @@
         <v>360.85</v>
       </c>
       <c r="M71">
-        <v>226.82025</v>
+        <v>230.1075</v>
       </c>
       <c r="N71">
-        <v>134.02975</v>
+        <v>130.7424999999999</v>
       </c>
       <c r="O71">
-        <v>40.20892499999999</v>
+        <v>39.22274999999998</v>
       </c>
       <c r="P71">
-        <v>93.82082499999996</v>
+        <v>91.51974999999995</v>
       </c>
       <c r="Q71">
-        <v>189.7208249999999</v>
+        <v>187.4197499999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1141383144337493</v>
+        <v>0.1161491097302447</v>
       </c>
       <c r="T71">
-        <v>1.578252065444557</v>
+        <v>1.624690755894796</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.590907337418065</v>
+        <v>1.568180089740664</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7414,22 +7414,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07894473291907339</v>
+        <v>0.07903658836368452</v>
       </c>
       <c r="C72">
-        <v>-275.5153211893958</v>
+        <v>-317.8383507759036</v>
       </c>
       <c r="D72">
-        <v>2097.934678810605</v>
+        <v>2092.136649224096</v>
       </c>
       <c r="E72">
-        <v>943.5500000000004</v>
+        <v>980.075</v>
       </c>
       <c r="F72">
-        <v>2556.75</v>
+        <v>2593.275</v>
       </c>
       <c r="G72">
         <v>183.3</v>
@@ -7450,28 +7450,28 @@
         <v>360.85</v>
       </c>
       <c r="M72">
-        <v>230.1075</v>
+        <v>233.39475</v>
       </c>
       <c r="N72">
-        <v>130.7424999999999</v>
+        <v>127.45525</v>
       </c>
       <c r="O72">
-        <v>39.22274999999998</v>
+        <v>38.23657499999999</v>
       </c>
       <c r="P72">
-        <v>91.51974999999995</v>
+        <v>89.21867499999999</v>
       </c>
       <c r="Q72">
-        <v>187.4197499999999</v>
+        <v>185.118675</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1161491097302447</v>
+        <v>0.1182985805644294</v>
       </c>
       <c r="T72">
-        <v>1.624690755894796</v>
+        <v>1.674332114651948</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.568180089740664</v>
+        <v>1.546093046223191</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7496,22 +7496,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0790365883636845</v>
+        <v>0.07912844380829562</v>
       </c>
       <c r="C73">
-        <v>-317.8383507759031</v>
+        <v>-360.1294208392715</v>
       </c>
       <c r="D73">
-        <v>2092.136649224097</v>
+        <v>2086.370579160728</v>
       </c>
       <c r="E73">
-        <v>980.075</v>
+        <v>1016.6</v>
       </c>
       <c r="F73">
-        <v>2593.275</v>
+        <v>2629.8</v>
       </c>
       <c r="G73">
         <v>183.3</v>
@@ -7532,28 +7532,28 @@
         <v>360.85</v>
       </c>
       <c r="M73">
-        <v>233.39475</v>
+        <v>236.682</v>
       </c>
       <c r="N73">
-        <v>127.45525</v>
+        <v>124.168</v>
       </c>
       <c r="O73">
-        <v>38.23657499999999</v>
+        <v>37.2504</v>
       </c>
       <c r="P73">
-        <v>89.21867499999999</v>
+        <v>86.91760000000001</v>
       </c>
       <c r="Q73">
-        <v>185.118675</v>
+        <v>182.8176</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1182985805644293</v>
+        <v>0.1206015850296272</v>
       </c>
       <c r="T73">
-        <v>1.674332114651948</v>
+        <v>1.727519284748896</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.546093046223191</v>
+        <v>1.524619531692313</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7578,22 +7578,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07912844380829562</v>
+        <v>0.07922029925290673</v>
       </c>
       <c r="C74">
-        <v>-360.1294208392715</v>
+        <v>-402.3887949010382</v>
       </c>
       <c r="D74">
-        <v>2086.370579160728</v>
+        <v>2080.636205098961</v>
       </c>
       <c r="E74">
-        <v>1016.6</v>
+        <v>1053.125</v>
       </c>
       <c r="F74">
-        <v>2629.8</v>
+        <v>2666.325</v>
       </c>
       <c r="G74">
         <v>183.3</v>
@@ -7614,28 +7614,28 @@
         <v>360.85</v>
       </c>
       <c r="M74">
-        <v>236.682</v>
+        <v>239.96925</v>
       </c>
       <c r="N74">
-        <v>124.168</v>
+        <v>120.88075</v>
       </c>
       <c r="O74">
-        <v>37.2504</v>
+        <v>36.26422499999999</v>
       </c>
       <c r="P74">
-        <v>86.91760000000001</v>
+        <v>84.616525</v>
       </c>
       <c r="Q74">
-        <v>182.8176</v>
+        <v>180.516525</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1206015850296272</v>
+        <v>0.1230751824181731</v>
       </c>
       <c r="T74">
-        <v>1.727519284748896</v>
+        <v>1.784646245223397</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.524619531692313</v>
+        <v>1.503734332628035</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7660,22 +7660,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07922029925290673</v>
+        <v>0.1122225770839134</v>
       </c>
       <c r="C75">
-        <v>-402.3887949010382</v>
+        <v>-1472.684797480179</v>
       </c>
       <c r="D75">
-        <v>2080.636205098961</v>
+        <v>1046.865202519821</v>
       </c>
       <c r="E75">
-        <v>1053.125</v>
+        <v>1089.65</v>
       </c>
       <c r="F75">
-        <v>2666.325</v>
+        <v>2702.85</v>
       </c>
       <c r="G75">
         <v>183.3</v>
@@ -7696,45 +7696,45 @@
         <v>360.85</v>
       </c>
       <c r="M75">
-        <v>239.96925</v>
+        <v>396.77838</v>
       </c>
       <c r="N75">
-        <v>120.88075</v>
+        <v>-35.92838000000006</v>
       </c>
       <c r="O75">
-        <v>36.26422499999999</v>
+        <v>-10.77851400000002</v>
       </c>
       <c r="P75">
-        <v>84.616525</v>
+        <v>-25.14986600000005</v>
       </c>
       <c r="Q75">
-        <v>180.516525</v>
+        <v>70.75013399999993</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1230751824181731</v>
+        <v>0.1278045414615846</v>
       </c>
       <c r="T75">
-        <v>1.784646245223397</v>
+        <v>1.893869317819507</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.3</v>
+        <v>0.2728349261368525</v>
       </c>
       <c r="W75">
-        <v>0.063</v>
+        <v>0.1067478328431101</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.503734332628035</v>
+        <v>0.9094497537895082</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7742,22 +7742,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1122225770839134</v>
+        <v>0.1132325770839135</v>
       </c>
       <c r="C76">
-        <v>-1472.684797480179</v>
+        <v>-1524.889664693756</v>
       </c>
       <c r="D76">
-        <v>1046.865202519821</v>
+        <v>1031.185335306244</v>
       </c>
       <c r="E76">
-        <v>1089.65</v>
+        <v>1126.175</v>
       </c>
       <c r="F76">
-        <v>2702.85</v>
+        <v>2739.375</v>
       </c>
       <c r="G76">
         <v>183.3</v>
@@ -7778,37 +7778,37 @@
         <v>360.85</v>
       </c>
       <c r="M76">
-        <v>396.77838</v>
+        <v>402.14025</v>
       </c>
       <c r="N76">
-        <v>-35.92838000000006</v>
+        <v>-41.29025000000007</v>
       </c>
       <c r="O76">
-        <v>-10.77851400000002</v>
+        <v>-12.38707500000002</v>
       </c>
       <c r="P76">
-        <v>-25.14986600000005</v>
+        <v>-28.90317500000005</v>
       </c>
       <c r="Q76">
-        <v>70.75013399999993</v>
+        <v>66.99682499999993</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1278045414615846</v>
+        <v>0.131084723120048</v>
       </c>
       <c r="T76">
-        <v>1.893869317819507</v>
+        <v>1.969624090532287</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2728349261368525</v>
+        <v>0.2691971271216944</v>
       </c>
       <c r="W76">
-        <v>0.1067478328431101</v>
+        <v>0.1072818617385353</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9094497537895082</v>
+        <v>0.8973237570723148</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7824,22 +7824,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1132325770839135</v>
+        <v>0.1142425770839135</v>
       </c>
       <c r="C77">
-        <v>-1524.889664693756</v>
+        <v>-1576.631759564137</v>
       </c>
       <c r="D77">
-        <v>1031.185335306244</v>
+        <v>1015.968240435863</v>
       </c>
       <c r="E77">
-        <v>1126.175</v>
+        <v>1162.7</v>
       </c>
       <c r="F77">
-        <v>2739.375</v>
+        <v>2775.9</v>
       </c>
       <c r="G77">
         <v>183.3</v>
@@ -7860,37 +7860,37 @@
         <v>360.85</v>
       </c>
       <c r="M77">
-        <v>402.14025</v>
+        <v>407.50212</v>
       </c>
       <c r="N77">
-        <v>-41.29025000000007</v>
+        <v>-46.65212000000008</v>
       </c>
       <c r="O77">
-        <v>-12.38707500000002</v>
+        <v>-13.99563600000002</v>
       </c>
       <c r="P77">
-        <v>-28.90317500000005</v>
+        <v>-32.65648400000006</v>
       </c>
       <c r="Q77">
-        <v>66.99682499999993</v>
+        <v>63.24351599999992</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.131084723120048</v>
+        <v>0.13463825325005</v>
       </c>
       <c r="T77">
-        <v>1.969624090532287</v>
+        <v>2.051691760971133</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2691971271216944</v>
+        <v>0.2656550596595669</v>
       </c>
       <c r="W77">
-        <v>0.1072818617385353</v>
+        <v>0.1078018372419756</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8973237570723148</v>
+        <v>0.8855168655318896</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7906,22 +7906,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1142425770839135</v>
+        <v>0.1152525770839135</v>
       </c>
       <c r="C78">
-        <v>-1576.631759564137</v>
+        <v>-1627.931271409831</v>
       </c>
       <c r="D78">
-        <v>1015.968240435863</v>
+        <v>1001.19372859017</v>
       </c>
       <c r="E78">
-        <v>1162.7</v>
+        <v>1199.225</v>
       </c>
       <c r="F78">
-        <v>2775.9</v>
+        <v>2812.425</v>
       </c>
       <c r="G78">
         <v>183.3</v>
@@ -7942,37 +7942,37 @@
         <v>360.85</v>
       </c>
       <c r="M78">
-        <v>407.50212</v>
+        <v>412.8639900000001</v>
       </c>
       <c r="N78">
-        <v>-46.65212000000008</v>
+        <v>-52.01399000000009</v>
       </c>
       <c r="O78">
-        <v>-13.99563600000002</v>
+        <v>-15.60419700000003</v>
       </c>
       <c r="P78">
-        <v>-32.65648400000006</v>
+        <v>-36.40979300000006</v>
       </c>
       <c r="Q78">
-        <v>63.24351599999992</v>
+        <v>59.49020699999991</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.13463825325005</v>
+        <v>0.1385007860000522</v>
       </c>
       <c r="T78">
-        <v>2.051691760971133</v>
+        <v>2.140895750578573</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2656550596595669</v>
+        <v>0.2622049939497024</v>
       </c>
       <c r="W78">
-        <v>0.1078018372419756</v>
+        <v>0.1083083068881837</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8855168655318896</v>
+        <v>0.8740166464990079</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7988,22 +7988,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1152525770839135</v>
+        <v>0.1162625770839135</v>
       </c>
       <c r="C79">
-        <v>-1627.931271409831</v>
+        <v>-1678.807231986703</v>
       </c>
       <c r="D79">
-        <v>1001.19372859017</v>
+        <v>986.8427680132974</v>
       </c>
       <c r="E79">
-        <v>1199.225</v>
+        <v>1235.75</v>
       </c>
       <c r="F79">
-        <v>2812.425</v>
+        <v>2848.95</v>
       </c>
       <c r="G79">
         <v>183.3</v>
@@ -8024,37 +8024,37 @@
         <v>360.85</v>
       </c>
       <c r="M79">
-        <v>412.8639900000001</v>
+        <v>418.2258600000001</v>
       </c>
       <c r="N79">
-        <v>-52.01399000000009</v>
+        <v>-57.3758600000001</v>
       </c>
       <c r="O79">
-        <v>-15.60419700000003</v>
+        <v>-17.21275800000003</v>
       </c>
       <c r="P79">
-        <v>-36.40979300000006</v>
+        <v>-40.16310200000007</v>
       </c>
       <c r="Q79">
-        <v>59.49020699999991</v>
+        <v>55.7368979999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1385007860000522</v>
+        <v>0.1427144580909637</v>
       </c>
       <c r="T79">
-        <v>2.140895750578573</v>
+        <v>2.23820919378669</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2622049939497024</v>
+        <v>0.2588433914631677</v>
       </c>
       <c r="W79">
-        <v>0.1083083068881837</v>
+        <v>0.108801790133207</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8740166464990079</v>
+        <v>0.8628113048772257</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8070,22 +8070,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1162625770839135</v>
+        <v>0.1172725770839135</v>
       </c>
       <c r="C80">
-        <v>-1678.807231986703</v>
+        <v>-1729.27759727727</v>
       </c>
       <c r="D80">
-        <v>986.8427680132974</v>
+        <v>972.89740272273</v>
       </c>
       <c r="E80">
-        <v>1235.75</v>
+        <v>1272.275</v>
       </c>
       <c r="F80">
-        <v>2848.95</v>
+        <v>2885.475</v>
       </c>
       <c r="G80">
         <v>183.3</v>
@@ -8106,37 +8106,37 @@
         <v>360.85</v>
       </c>
       <c r="M80">
-        <v>418.2258600000001</v>
+        <v>423.58773</v>
       </c>
       <c r="N80">
-        <v>-57.3758600000001</v>
+        <v>-62.73773000000006</v>
       </c>
       <c r="O80">
-        <v>-17.21275800000003</v>
+        <v>-18.82131900000002</v>
       </c>
       <c r="P80">
-        <v>-40.16310200000007</v>
+        <v>-43.91641100000004</v>
       </c>
       <c r="Q80">
-        <v>55.7368979999999</v>
+        <v>51.98358899999994</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1427144580909637</v>
+        <v>0.1473294322857715</v>
       </c>
       <c r="T80">
-        <v>2.23820919378669</v>
+        <v>2.344790583967009</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2588433914631677</v>
+        <v>0.2555668928370517</v>
       </c>
       <c r="W80">
-        <v>0.108801790133207</v>
+        <v>0.1092827801315208</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8628113048772257</v>
+        <v>0.8518896427901723</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8152,22 +8152,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1172725770839135</v>
+        <v>0.1182825770839135</v>
       </c>
       <c r="C81">
-        <v>-1729.27759727727</v>
+        <v>-1779.35932244189</v>
       </c>
       <c r="D81">
-        <v>972.89740272273</v>
+        <v>959.3406775581103</v>
       </c>
       <c r="E81">
-        <v>1272.275</v>
+        <v>1308.8</v>
       </c>
       <c r="F81">
-        <v>2885.475</v>
+        <v>2922</v>
       </c>
       <c r="G81">
         <v>183.3</v>
@@ -8188,37 +8188,37 @@
         <v>360.85</v>
       </c>
       <c r="M81">
-        <v>423.58773</v>
+        <v>428.9496</v>
       </c>
       <c r="N81">
-        <v>-62.73773000000006</v>
+        <v>-68.09960000000007</v>
       </c>
       <c r="O81">
-        <v>-18.82131900000002</v>
+        <v>-20.42988000000002</v>
       </c>
       <c r="P81">
-        <v>-43.91641100000004</v>
+        <v>-47.66972000000005</v>
       </c>
       <c r="Q81">
-        <v>51.98358899999994</v>
+        <v>48.23027999999993</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1473294322857715</v>
+        <v>0.1524059039000601</v>
       </c>
       <c r="T81">
-        <v>2.344790583967009</v>
+        <v>2.462030113165359</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2555668928370517</v>
+        <v>0.2523723066765885</v>
       </c>
       <c r="W81">
-        <v>0.1092827801315208</v>
+        <v>0.1097517453798768</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8518896427901723</v>
+        <v>0.8412410222552951</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8234,22 +8234,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1182825770839135</v>
+        <v>0.1192925770839134</v>
       </c>
       <c r="C82">
-        <v>-1779.35932244189</v>
+        <v>-1829.068430589674</v>
       </c>
       <c r="D82">
-        <v>959.3406775581103</v>
+        <v>946.1565694103263</v>
       </c>
       <c r="E82">
-        <v>1308.8</v>
+        <v>1345.325</v>
       </c>
       <c r="F82">
-        <v>2922</v>
+        <v>2958.525</v>
       </c>
       <c r="G82">
         <v>183.3</v>
@@ -8270,37 +8270,37 @@
         <v>360.85</v>
       </c>
       <c r="M82">
-        <v>428.9496</v>
+        <v>434.31147</v>
       </c>
       <c r="N82">
-        <v>-68.09960000000007</v>
+        <v>-73.46147000000008</v>
       </c>
       <c r="O82">
-        <v>-20.42988000000002</v>
+        <v>-22.03844100000002</v>
       </c>
       <c r="P82">
-        <v>-47.66972000000005</v>
+        <v>-51.42302900000006</v>
       </c>
       <c r="Q82">
-        <v>48.23027999999993</v>
+        <v>44.47697099999992</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1524059039000601</v>
+        <v>0.1580167409474316</v>
       </c>
       <c r="T82">
-        <v>2.462030113165359</v>
+        <v>2.59161064543722</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2523723066765885</v>
+        <v>0.2492565991867541</v>
       </c>
       <c r="W82">
-        <v>0.1097517453798768</v>
+        <v>0.1102091312393845</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8412410222552951</v>
+        <v>0.8308553306225137</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8316,22 +8316,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1192925770839134</v>
+        <v>0.1203025770839135</v>
       </c>
       <c r="C83">
-        <v>-1829.068430589674</v>
+        <v>-1878.42007595562</v>
       </c>
       <c r="D83">
-        <v>946.1565694103263</v>
+        <v>933.3299240443797</v>
       </c>
       <c r="E83">
-        <v>1345.325</v>
+        <v>1381.85</v>
       </c>
       <c r="F83">
-        <v>2958.525</v>
+        <v>2995.05</v>
       </c>
       <c r="G83">
         <v>183.3</v>
@@ -8352,37 +8352,37 @@
         <v>360.85</v>
       </c>
       <c r="M83">
-        <v>434.31147</v>
+        <v>439.6733400000001</v>
       </c>
       <c r="N83">
-        <v>-73.46147000000008</v>
+        <v>-78.82334000000009</v>
       </c>
       <c r="O83">
-        <v>-22.03844100000002</v>
+        <v>-23.64700200000003</v>
       </c>
       <c r="P83">
-        <v>-51.42302900000006</v>
+        <v>-55.17633800000006</v>
       </c>
       <c r="Q83">
-        <v>44.47697099999992</v>
+        <v>40.72366199999992</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1580167409474316</v>
+        <v>0.1642510043334001</v>
       </c>
       <c r="T83">
-        <v>2.59161064543722</v>
+        <v>2.735589014628177</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2492565991867541</v>
+        <v>0.2462168845625254</v>
       </c>
       <c r="W83">
-        <v>0.1102091312393845</v>
+        <v>0.1106553613462213</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8308553306225137</v>
+        <v>0.8207229485417513</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8398,22 +8398,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1203025770839135</v>
+        <v>0.1213125770839135</v>
       </c>
       <c r="C84">
-        <v>-1878.42007595562</v>
+        <v>-1927.428602007675</v>
       </c>
       <c r="D84">
-        <v>933.3299240443797</v>
+        <v>920.846397992325</v>
       </c>
       <c r="E84">
-        <v>1381.85</v>
+        <v>1418.375</v>
       </c>
       <c r="F84">
-        <v>2995.05</v>
+        <v>3031.575</v>
       </c>
       <c r="G84">
         <v>183.3</v>
@@ -8434,37 +8434,37 @@
         <v>360.85</v>
       </c>
       <c r="M84">
-        <v>439.6733400000001</v>
+        <v>445.0352100000001</v>
       </c>
       <c r="N84">
-        <v>-78.82334000000009</v>
+        <v>-84.1852100000001</v>
       </c>
       <c r="O84">
-        <v>-23.64700200000003</v>
+        <v>-25.25556300000003</v>
       </c>
       <c r="P84">
-        <v>-55.17633800000006</v>
+        <v>-58.92964700000007</v>
       </c>
       <c r="Q84">
-        <v>40.72366199999992</v>
+        <v>36.9703529999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1642510043334001</v>
+        <v>0.171218710470659</v>
       </c>
       <c r="T84">
-        <v>2.735589014628177</v>
+        <v>2.896506015488659</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2462168845625254</v>
+        <v>0.2432504160738203</v>
       </c>
       <c r="W84">
-        <v>0.1106553613462213</v>
+        <v>0.1110908389203632</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8207229485417513</v>
+        <v>0.8108347202460675</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8480,22 +8480,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1213125770839135</v>
+        <v>0.1223225770839135</v>
       </c>
       <c r="C85">
-        <v>-1927.428602007675</v>
+        <v>-1976.107594952168</v>
       </c>
       <c r="D85">
-        <v>920.846397992325</v>
+        <v>908.6924050478325</v>
       </c>
       <c r="E85">
-        <v>1418.375</v>
+        <v>1454.9</v>
       </c>
       <c r="F85">
-        <v>3031.575</v>
+        <v>3068.1</v>
       </c>
       <c r="G85">
         <v>183.3</v>
@@ -8516,37 +8516,37 @@
         <v>360.85</v>
       </c>
       <c r="M85">
-        <v>445.0352100000001</v>
+        <v>450.3970800000001</v>
       </c>
       <c r="N85">
-        <v>-84.1852100000001</v>
+        <v>-89.54708000000011</v>
       </c>
       <c r="O85">
-        <v>-25.25556300000003</v>
+        <v>-26.86412400000003</v>
       </c>
       <c r="P85">
-        <v>-58.92964700000007</v>
+        <v>-62.68295600000008</v>
       </c>
       <c r="Q85">
-        <v>36.9703529999999</v>
+        <v>33.2170439999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.171218710470659</v>
+        <v>0.1790573798750752</v>
       </c>
       <c r="T85">
-        <v>2.896506015488659</v>
+        <v>3.077537641456701</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2432504160738203</v>
+        <v>0.2403545777872272</v>
       </c>
       <c r="W85">
-        <v>0.1110908389203632</v>
+        <v>0.1115159479808351</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8108347202460675</v>
+        <v>0.8011819259574239</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8562,22 +8562,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1223225770839135</v>
+        <v>0.1706830663014399</v>
       </c>
       <c r="C86">
-        <v>-1976.107594952167</v>
+        <v>-2364.520249202191</v>
       </c>
       <c r="D86">
-        <v>908.6924050478333</v>
+        <v>556.8047507978091</v>
       </c>
       <c r="E86">
-        <v>1454.9</v>
+        <v>1491.425</v>
       </c>
       <c r="F86">
-        <v>3068.1</v>
+        <v>3104.625</v>
       </c>
       <c r="G86">
         <v>183.3</v>
@@ -8598,45 +8598,45 @@
         <v>360.85</v>
       </c>
       <c r="M86">
-        <v>450.39708</v>
+        <v>623.4087000000001</v>
       </c>
       <c r="N86">
-        <v>-89.54708000000005</v>
+        <v>-262.5587000000001</v>
       </c>
       <c r="O86">
-        <v>-26.86412400000001</v>
+        <v>-78.76761000000003</v>
       </c>
       <c r="P86">
-        <v>-62.68295600000003</v>
+        <v>-183.7910900000001</v>
       </c>
       <c r="Q86">
-        <v>33.21704399999994</v>
+        <v>-87.89109000000008</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1790573798750751</v>
+        <v>0.1976111333169228</v>
       </c>
       <c r="T86">
-        <v>3.077537641456699</v>
+        <v>3.506030792538634</v>
       </c>
       <c r="U86">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.2403545777872272</v>
+        <v>0.1736501271156466</v>
       </c>
       <c r="W86">
-        <v>0.1115159479808351</v>
+        <v>0.1659310544751782</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.801181925957424</v>
+        <v>0.5788337570521552</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8644,22 +8644,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1706830663014399</v>
+        <v>0.1722330663014399</v>
       </c>
       <c r="C87">
-        <v>-2364.520249202191</v>
+        <v>-2407.871369844389</v>
       </c>
       <c r="D87">
-        <v>556.8047507978091</v>
+        <v>549.9786301556113</v>
       </c>
       <c r="E87">
-        <v>1491.425</v>
+        <v>1527.95</v>
       </c>
       <c r="F87">
-        <v>3104.625</v>
+        <v>3141.15</v>
       </c>
       <c r="G87">
         <v>183.3</v>
@@ -8680,37 +8680,37 @@
         <v>360.85</v>
       </c>
       <c r="M87">
-        <v>623.4087000000001</v>
+        <v>630.74292</v>
       </c>
       <c r="N87">
-        <v>-262.5587000000001</v>
+        <v>-269.8929200000001</v>
       </c>
       <c r="O87">
-        <v>-78.76761000000003</v>
+        <v>-80.96787600000002</v>
       </c>
       <c r="P87">
-        <v>-183.7910900000001</v>
+        <v>-188.925044</v>
       </c>
       <c r="Q87">
-        <v>-87.89109000000008</v>
+        <v>-93.02504400000007</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1976111333169228</v>
+        <v>0.2084547856967031</v>
       </c>
       <c r="T87">
-        <v>3.506030792538634</v>
+        <v>3.756461563434251</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1736501271156466</v>
+        <v>0.1716309395910461</v>
       </c>
       <c r="W87">
-        <v>0.1659310544751782</v>
+        <v>0.166336507330118</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5788337570521552</v>
+        <v>0.5721031319701535</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8726,22 +8726,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1722330663014399</v>
+        <v>0.1737830663014399</v>
       </c>
       <c r="C88">
-        <v>-2407.871369844389</v>
+        <v>-2451.057148503445</v>
       </c>
       <c r="D88">
-        <v>549.9786301556113</v>
+        <v>543.3178514965551</v>
       </c>
       <c r="E88">
-        <v>1527.95</v>
+        <v>1564.475</v>
       </c>
       <c r="F88">
-        <v>3141.15</v>
+        <v>3177.675</v>
       </c>
       <c r="G88">
         <v>183.3</v>
@@ -8762,37 +8762,37 @@
         <v>360.85</v>
       </c>
       <c r="M88">
-        <v>630.74292</v>
+        <v>638.0771400000001</v>
       </c>
       <c r="N88">
-        <v>-269.8929200000001</v>
+        <v>-277.2271400000001</v>
       </c>
       <c r="O88">
-        <v>-80.96787600000002</v>
+        <v>-83.16814200000003</v>
       </c>
       <c r="P88">
-        <v>-188.925044</v>
+        <v>-194.0589980000001</v>
       </c>
       <c r="Q88">
-        <v>-93.02504400000007</v>
+        <v>-98.15899800000011</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2084547856967031</v>
+        <v>0.2209666922887571</v>
       </c>
       <c r="T88">
-        <v>3.756461563434251</v>
+        <v>4.045420145236886</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1716309395910461</v>
+        <v>0.1696581701704593</v>
       </c>
       <c r="W88">
-        <v>0.166336507330118</v>
+        <v>0.1667326394297718</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5721031319701535</v>
+        <v>0.5655272339015309</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8808,22 +8808,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1737830663014399</v>
+        <v>0.1753330663014399</v>
       </c>
       <c r="C89">
-        <v>-2451.057148503445</v>
+        <v>-2494.083520653934</v>
       </c>
       <c r="D89">
-        <v>543.3178514965551</v>
+        <v>536.8164793460659</v>
       </c>
       <c r="E89">
-        <v>1564.475</v>
+        <v>1601</v>
       </c>
       <c r="F89">
-        <v>3177.675</v>
+        <v>3214.2</v>
       </c>
       <c r="G89">
         <v>183.3</v>
@@ -8844,37 +8844,37 @@
         <v>360.85</v>
       </c>
       <c r="M89">
-        <v>638.0771400000001</v>
+        <v>645.4113599999999</v>
       </c>
       <c r="N89">
-        <v>-277.2271400000001</v>
+        <v>-284.56136</v>
       </c>
       <c r="O89">
-        <v>-83.16814200000003</v>
+        <v>-85.36840799999999</v>
       </c>
       <c r="P89">
-        <v>-194.0589980000001</v>
+        <v>-199.192952</v>
       </c>
       <c r="Q89">
-        <v>-98.15899800000011</v>
+        <v>-103.292952</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2209666922887571</v>
+        <v>0.2355639166461536</v>
       </c>
       <c r="T89">
-        <v>4.045420145236886</v>
+        <v>4.382538490673292</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1696581701704593</v>
+        <v>0.1677302364185223</v>
       </c>
       <c r="W89">
-        <v>0.1667326394297718</v>
+        <v>0.1671197685271607</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5655272339015309</v>
+        <v>0.5591007880617409</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8890,22 +8890,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1753330663014399</v>
+        <v>0.1768830663014399</v>
       </c>
       <c r="C90">
-        <v>-2494.083520653934</v>
+        <v>-2536.956141032854</v>
       </c>
       <c r="D90">
-        <v>536.8164793460659</v>
+        <v>530.4688589671455</v>
       </c>
       <c r="E90">
-        <v>1601</v>
+        <v>1637.525</v>
       </c>
       <c r="F90">
-        <v>3214.2</v>
+        <v>3250.725</v>
       </c>
       <c r="G90">
         <v>183.3</v>
@@ -8926,37 +8926,37 @@
         <v>360.85</v>
       </c>
       <c r="M90">
-        <v>645.4113599999999</v>
+        <v>652.74558</v>
       </c>
       <c r="N90">
-        <v>-284.56136</v>
+        <v>-291.8955800000001</v>
       </c>
       <c r="O90">
-        <v>-85.36840799999999</v>
+        <v>-87.56867400000002</v>
       </c>
       <c r="P90">
-        <v>-199.192952</v>
+        <v>-204.326906</v>
       </c>
       <c r="Q90">
-        <v>-103.292952</v>
+        <v>-108.4269060000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2355639166461536</v>
+        <v>0.2528151817958039</v>
       </c>
       <c r="T90">
-        <v>4.382538490673292</v>
+        <v>4.780951080734501</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1677302364185223</v>
+        <v>0.1658456270205614</v>
       </c>
       <c r="W90">
-        <v>0.1671197685271607</v>
+        <v>0.1674981980942713</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5591007880617409</v>
+        <v>0.5528187567352045</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8972,22 +8972,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1768830663014399</v>
+        <v>0.1784330663014399</v>
       </c>
       <c r="C91">
-        <v>-2536.956141032854</v>
+        <v>-2579.680400043653</v>
       </c>
       <c r="D91">
-        <v>530.4688589671455</v>
+        <v>524.2695999563467</v>
       </c>
       <c r="E91">
-        <v>1637.525</v>
+        <v>1674.05</v>
       </c>
       <c r="F91">
-        <v>3250.725</v>
+        <v>3287.25</v>
       </c>
       <c r="G91">
         <v>183.3</v>
@@ -9008,37 +9008,37 @@
         <v>360.85</v>
       </c>
       <c r="M91">
-        <v>652.74558</v>
+        <v>660.0798</v>
       </c>
       <c r="N91">
-        <v>-291.8955800000001</v>
+        <v>-299.2298</v>
       </c>
       <c r="O91">
-        <v>-87.56867400000002</v>
+        <v>-89.76894</v>
       </c>
       <c r="P91">
-        <v>-204.326906</v>
+        <v>-209.46086</v>
       </c>
       <c r="Q91">
-        <v>-108.4269060000001</v>
+        <v>-113.56086</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2528151817958039</v>
+        <v>0.2735166999753844</v>
       </c>
       <c r="T91">
-        <v>4.780951080734501</v>
+        <v>5.259046188807953</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1658456270205614</v>
+        <v>0.164002897831444</v>
       </c>
       <c r="W91">
-        <v>0.1674981980942713</v>
+        <v>0.1678682181154461</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5528187567352045</v>
+        <v>0.5466763261048133</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9054,22 +9054,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1784330663014399</v>
+        <v>0.1799830663014399</v>
       </c>
       <c r="C92">
-        <v>-2579.680400043653</v>
+        <v>-2622.261439023318</v>
       </c>
       <c r="D92">
-        <v>524.2695999563467</v>
+        <v>518.2135609766829</v>
       </c>
       <c r="E92">
-        <v>1674.05</v>
+        <v>1710.575</v>
       </c>
       <c r="F92">
-        <v>3287.25</v>
+        <v>3323.775</v>
       </c>
       <c r="G92">
         <v>183.3</v>
@@ -9090,37 +9090,37 @@
         <v>360.85</v>
       </c>
       <c r="M92">
-        <v>660.0798</v>
+        <v>667.4140200000001</v>
       </c>
       <c r="N92">
-        <v>-299.2298</v>
+        <v>-306.5640200000001</v>
       </c>
       <c r="O92">
-        <v>-89.76894</v>
+        <v>-91.96920600000003</v>
       </c>
       <c r="P92">
-        <v>-209.46086</v>
+        <v>-214.594814</v>
       </c>
       <c r="Q92">
-        <v>-113.56086</v>
+        <v>-118.6948140000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2735166999753844</v>
+        <v>0.2988185555282049</v>
       </c>
       <c r="T92">
-        <v>5.259046188807953</v>
+        <v>5.843384654231059</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.164002897831444</v>
+        <v>0.1622006681849446</v>
       </c>
       <c r="W92">
-        <v>0.1678682181154461</v>
+        <v>0.1682301058284631</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5466763261048133</v>
+        <v>0.5406688939498153</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9136,22 +9136,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1799830663014399</v>
+        <v>0.1815330663014399</v>
       </c>
       <c r="C93">
-        <v>-2622.261439023318</v>
+        <v>-2664.704164463411</v>
       </c>
       <c r="D93">
-        <v>518.2135609766829</v>
+        <v>512.2958355365897</v>
       </c>
       <c r="E93">
-        <v>1710.575</v>
+        <v>1747.1</v>
       </c>
       <c r="F93">
-        <v>3323.775</v>
+        <v>3360.3</v>
       </c>
       <c r="G93">
         <v>183.3</v>
@@ -9172,37 +9172,37 @@
         <v>360.85</v>
       </c>
       <c r="M93">
-        <v>667.4140200000001</v>
+        <v>674.74824</v>
       </c>
       <c r="N93">
-        <v>-306.5640200000001</v>
+        <v>-313.89824</v>
       </c>
       <c r="O93">
-        <v>-91.96920600000003</v>
+        <v>-94.16947200000001</v>
       </c>
       <c r="P93">
-        <v>-214.594814</v>
+        <v>-219.728768</v>
       </c>
       <c r="Q93">
-        <v>-118.6948140000001</v>
+        <v>-123.8287680000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2988185555282049</v>
+        <v>0.3304458749692305</v>
       </c>
       <c r="T93">
-        <v>5.843384654231059</v>
+        <v>6.573807736009942</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1622006681849446</v>
+        <v>0.1604376174438039</v>
       </c>
       <c r="W93">
-        <v>0.1682301058284631</v>
+        <v>0.1685841264172842</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5406688939498153</v>
+        <v>0.534792058146013</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9218,22 +9218,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1815330663014399</v>
+        <v>0.1830830663014399</v>
       </c>
       <c r="C94">
-        <v>-2664.704164463411</v>
+        <v>-2707.013261267733</v>
       </c>
       <c r="D94">
-        <v>512.2958355365897</v>
+        <v>506.5117387322676</v>
       </c>
       <c r="E94">
-        <v>1747.1</v>
+        <v>1783.625</v>
       </c>
       <c r="F94">
-        <v>3360.3</v>
+        <v>3396.825</v>
       </c>
       <c r="G94">
         <v>183.3</v>
@@ -9254,37 +9254,37 @@
         <v>360.85</v>
       </c>
       <c r="M94">
-        <v>674.74824</v>
+        <v>682.0824600000001</v>
       </c>
       <c r="N94">
-        <v>-313.89824</v>
+        <v>-321.2324600000001</v>
       </c>
       <c r="O94">
-        <v>-94.16947200000001</v>
+        <v>-96.36973800000003</v>
       </c>
       <c r="P94">
-        <v>-219.728768</v>
+        <v>-224.8627220000001</v>
       </c>
       <c r="Q94">
-        <v>-123.8287680000001</v>
+        <v>-128.9627220000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3304458749692305</v>
+        <v>0.3711095713934063</v>
       </c>
       <c r="T94">
-        <v>6.573807736009942</v>
+        <v>7.512923126868507</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1604376174438039</v>
+        <v>0.1587124817723652</v>
       </c>
       <c r="W94">
-        <v>0.1685841264172842</v>
+        <v>0.1689305336601091</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.534792058146013</v>
+        <v>0.5290416059078837</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9300,22 +9300,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1830830663014399</v>
+        <v>0.1846330663014399</v>
       </c>
       <c r="C95">
-        <v>-2707.013261267733</v>
+        <v>-2749.193205121889</v>
       </c>
       <c r="D95">
-        <v>506.5117387322676</v>
+        <v>500.8567948781112</v>
       </c>
       <c r="E95">
-        <v>1783.625</v>
+        <v>1820.15</v>
       </c>
       <c r="F95">
-        <v>3396.825</v>
+        <v>3433.35</v>
       </c>
       <c r="G95">
         <v>183.3</v>
@@ -9336,37 +9336,37 @@
         <v>360.85</v>
       </c>
       <c r="M95">
-        <v>682.0824600000001</v>
+        <v>689.41668</v>
       </c>
       <c r="N95">
-        <v>-321.2324600000001</v>
+        <v>-328.5666800000001</v>
       </c>
       <c r="O95">
-        <v>-96.36973800000003</v>
+        <v>-98.57000400000003</v>
       </c>
       <c r="P95">
-        <v>-224.8627220000001</v>
+        <v>-229.996676</v>
       </c>
       <c r="Q95">
-        <v>-128.9627220000001</v>
+        <v>-134.0966760000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3711095713934063</v>
+        <v>0.4253278332923075</v>
       </c>
       <c r="T95">
-        <v>7.512923126868507</v>
+        <v>8.765076981346594</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1587124817723652</v>
+        <v>0.1570240511152123</v>
       </c>
       <c r="W95">
-        <v>0.1689305336601091</v>
+        <v>0.1692695705360654</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5290416059078837</v>
+        <v>0.5234135037173744</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9382,22 +9382,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1846330663014399</v>
+        <v>0.1861830663014399</v>
       </c>
       <c r="C96">
-        <v>-2749.193205121889</v>
+        <v>-2791.248274043408</v>
       </c>
       <c r="D96">
-        <v>500.8567948781112</v>
+        <v>495.3267259565927</v>
       </c>
       <c r="E96">
-        <v>1820.15</v>
+        <v>1856.675</v>
       </c>
       <c r="F96">
-        <v>3433.35</v>
+        <v>3469.875</v>
       </c>
       <c r="G96">
         <v>183.3</v>
@@ -9418,37 +9418,37 @@
         <v>360.85</v>
       </c>
       <c r="M96">
-        <v>689.41668</v>
+        <v>696.7509000000001</v>
       </c>
       <c r="N96">
-        <v>-328.5666800000001</v>
+        <v>-335.9009000000001</v>
       </c>
       <c r="O96">
-        <v>-98.57000400000003</v>
+        <v>-100.77027</v>
       </c>
       <c r="P96">
-        <v>-229.996676</v>
+        <v>-235.1306300000001</v>
       </c>
       <c r="Q96">
-        <v>-134.0966760000001</v>
+        <v>-139.2306300000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4253278332923075</v>
+        <v>0.5012333999507692</v>
       </c>
       <c r="T96">
-        <v>8.765076981346594</v>
+        <v>10.51809237761592</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1570240511152123</v>
+        <v>0.1553711663666311</v>
       </c>
       <c r="W96">
-        <v>0.1692695705360654</v>
+        <v>0.1696014697935805</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5234135037173744</v>
+        <v>0.5179038878887705</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9464,22 +9464,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1861830663014399</v>
+        <v>0.1877330663014399</v>
       </c>
       <c r="C97">
-        <v>-2791.248274043408</v>
+        <v>-2833.182559175049</v>
       </c>
       <c r="D97">
-        <v>495.3267259565927</v>
+        <v>489.9174408249506</v>
       </c>
       <c r="E97">
-        <v>1856.675</v>
+        <v>1893.2</v>
       </c>
       <c r="F97">
-        <v>3469.875</v>
+        <v>3506.4</v>
       </c>
       <c r="G97">
         <v>183.3</v>
@@ -9500,37 +9500,37 @@
         <v>360.85</v>
       </c>
       <c r="M97">
-        <v>696.7509000000001</v>
+        <v>704.0851200000001</v>
       </c>
       <c r="N97">
-        <v>-335.9009000000001</v>
+        <v>-343.2351200000001</v>
       </c>
       <c r="O97">
-        <v>-100.77027</v>
+        <v>-102.970536</v>
       </c>
       <c r="P97">
-        <v>-235.1306300000001</v>
+        <v>-240.2645840000001</v>
       </c>
       <c r="Q97">
-        <v>-139.2306300000001</v>
+        <v>-144.3645840000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5012333999507692</v>
+        <v>0.6150917499384617</v>
       </c>
       <c r="T97">
-        <v>10.51809237761592</v>
+        <v>13.1476154720199</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1553711663666311</v>
+        <v>0.1537527167169787</v>
       </c>
       <c r="W97">
-        <v>0.1696014697935805</v>
+        <v>0.1699264544832307</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5179038878887705</v>
+        <v>0.5125090557232624</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9546,22 +9546,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1877330663014399</v>
+        <v>0.1892830663014399</v>
       </c>
       <c r="C98">
-        <v>-2833.182559175049</v>
+        <v>-2874.999974878539</v>
       </c>
       <c r="D98">
-        <v>489.9174408249506</v>
+        <v>484.6250251214607</v>
       </c>
       <c r="E98">
-        <v>1893.2</v>
+        <v>1929.725</v>
       </c>
       <c r="F98">
-        <v>3506.4</v>
+        <v>3542.925</v>
       </c>
       <c r="G98">
         <v>183.3</v>
@@ -9582,37 +9582,37 @@
         <v>360.85</v>
       </c>
       <c r="M98">
-        <v>704.0851200000001</v>
+        <v>711.4193399999999</v>
       </c>
       <c r="N98">
-        <v>-343.2351200000001</v>
+        <v>-350.56934</v>
       </c>
       <c r="O98">
-        <v>-102.970536</v>
+        <v>-105.170802</v>
       </c>
       <c r="P98">
-        <v>-240.2645840000001</v>
+        <v>-245.398538</v>
       </c>
       <c r="Q98">
-        <v>-144.3645840000001</v>
+        <v>-149.498538</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6150917499384601</v>
+        <v>0.8048556665846136</v>
       </c>
       <c r="T98">
-        <v>13.14761547201987</v>
+        <v>17.53015396269316</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1537527167169787</v>
+        <v>0.1521676371631955</v>
       </c>
       <c r="W98">
-        <v>0.1699264544832307</v>
+        <v>0.1702447384576304</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5125090557232624</v>
+        <v>0.5072254572106516</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9628,22 +9628,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1892830663014399</v>
+        <v>0.1908330663014399</v>
       </c>
       <c r="C99">
-        <v>-2874.999974878539</v>
+        <v>-2916.704268181054</v>
       </c>
       <c r="D99">
-        <v>484.6250251214607</v>
+        <v>479.4457318189454</v>
       </c>
       <c r="E99">
-        <v>1929.725</v>
+        <v>1966.25</v>
       </c>
       <c r="F99">
-        <v>3542.925</v>
+        <v>3579.45</v>
       </c>
       <c r="G99">
         <v>183.3</v>
@@ -9664,37 +9664,37 @@
         <v>360.85</v>
       </c>
       <c r="M99">
-        <v>711.4193399999999</v>
+        <v>718.75356</v>
       </c>
       <c r="N99">
-        <v>-350.56934</v>
+        <v>-357.90356</v>
       </c>
       <c r="O99">
-        <v>-105.170802</v>
+        <v>-107.371068</v>
       </c>
       <c r="P99">
-        <v>-245.398538</v>
+        <v>-250.532492</v>
       </c>
       <c r="Q99">
-        <v>-149.498538</v>
+        <v>-154.632492</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8048556665846136</v>
+        <v>1.184383499876921</v>
       </c>
       <c r="T99">
-        <v>17.53015396269316</v>
+        <v>26.29523094403974</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1521676371631955</v>
+        <v>0.1506149061717343</v>
       </c>
       <c r="W99">
-        <v>0.1702447384576304</v>
+        <v>0.1705565268407158</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5072254572106516</v>
+        <v>0.5020496872391143</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9710,22 +9710,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1908330663014399</v>
+        <v>0.2276183562206786</v>
       </c>
       <c r="C100">
-        <v>-2916.704268181054</v>
+        <v>-3050.230201486685</v>
       </c>
       <c r="D100">
-        <v>479.4457318189454</v>
+        <v>382.4447985133145</v>
       </c>
       <c r="E100">
-        <v>1966.25</v>
+        <v>2002.775</v>
       </c>
       <c r="F100">
-        <v>3579.45</v>
+        <v>3615.975</v>
       </c>
       <c r="G100">
         <v>183.3</v>
@@ -9746,129 +9746,47 @@
         <v>360.85</v>
       </c>
       <c r="M100">
-        <v>718.75356</v>
+        <v>852.6469050000001</v>
       </c>
       <c r="N100">
-        <v>-357.90356</v>
+        <v>-491.7969050000001</v>
       </c>
       <c r="O100">
-        <v>-107.371068</v>
+        <v>-147.5390715</v>
       </c>
       <c r="P100">
-        <v>-250.532492</v>
+        <v>-344.2578335000001</v>
       </c>
       <c r="Q100">
-        <v>-154.632492</v>
+        <v>-248.3578335000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.184383499876921</v>
+        <v>2.381495991677715</v>
       </c>
       <c r="T100">
-        <v>26.29523094403974</v>
+        <v>53.94217070849227</v>
       </c>
       <c r="U100">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1506149061717343</v>
+        <v>0.1269634585725729</v>
       </c>
       <c r="W100">
-        <v>0.1705565268407158</v>
+        <v>0.2058620164685873</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5020496872391143</v>
+        <v>0.4232115285752429</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2276183562206786</v>
-      </c>
-      <c r="C101">
-        <v>-3050.230201486685</v>
-      </c>
-      <c r="D101">
-        <v>382.4447985133145</v>
-      </c>
-      <c r="E101">
-        <v>2002.775</v>
-      </c>
-      <c r="F101">
-        <v>3615.975</v>
-      </c>
-      <c r="G101">
-        <v>183.3</v>
-      </c>
-      <c r="H101">
-        <v>2039.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>456.7499999999999</v>
-      </c>
-      <c r="K101">
-        <v>95.89999999999998</v>
-      </c>
-      <c r="L101">
-        <v>360.85</v>
-      </c>
-      <c r="M101">
-        <v>852.6469050000001</v>
-      </c>
-      <c r="N101">
-        <v>-491.7969050000001</v>
-      </c>
-      <c r="O101">
-        <v>-147.5390715</v>
-      </c>
-      <c r="P101">
-        <v>-344.2578335000001</v>
-      </c>
-      <c r="Q101">
-        <v>-248.3578335000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.381495991677715</v>
-      </c>
-      <c r="T101">
-        <v>53.94217070849227</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1269634585725729</v>
-      </c>
-      <c r="W101">
-        <v>0.2058620164685873</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4232115285752429</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
